--- a/6月顔合わせ企画書_改善版.xlsx
+++ b/6月顔合わせ企画書_改善版.xlsx
@@ -12,6 +12,7 @@
     <sheet name="内定承諾者" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="目的" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="【改善版】6月顔合わせ企画書" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="【改善版v2】6月企画書" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191028" fullCalcOnLoad="1"/>
@@ -21,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="31">
+  <fonts count="32">
     <font>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
@@ -233,8 +234,12 @@
       <b val="1"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -295,8 +300,20 @@
         <bgColor rgb="00E8F4FD"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAD1DC"/>
+        <bgColor rgb="00EAD1DC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAD3"/>
+        <bgColor rgb="00D9EAD3"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="28">
+  <borders count="32">
     <border>
       <left/>
       <right/>
@@ -620,11 +637,55 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="105">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -812,6 +873,44 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="6" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="8" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="5" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="9" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="11" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="12" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="7" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="8" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="11" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3168,13 +3267,13 @@
           <t>27新卒 内定承諾者向け 顔合わせ企画書（Zoom・60分）</t>
         </is>
       </c>
-      <c r="B1" s="71" t="n"/>
-      <c r="C1" s="71" t="n"/>
-      <c r="D1" s="71" t="n"/>
-      <c r="E1" s="71" t="n"/>
-      <c r="F1" s="71" t="n"/>
-      <c r="G1" s="71" t="n"/>
-      <c r="H1" s="71" t="n"/>
+      <c r="B1" s="91" t="n"/>
+      <c r="C1" s="91" t="n"/>
+      <c r="D1" s="91" t="n"/>
+      <c r="E1" s="91" t="n"/>
+      <c r="F1" s="91" t="n"/>
+      <c r="G1" s="91" t="n"/>
+      <c r="H1" s="92" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="72" t="inlineStr">
@@ -3182,13 +3281,13 @@
           <t>参加者：内定承諾者 各グループ ＋ 人事担当　／　形式：Zoom　／　総時間：55〜60分</t>
         </is>
       </c>
-      <c r="B2" s="71" t="n"/>
-      <c r="C2" s="71" t="n"/>
-      <c r="D2" s="71" t="n"/>
-      <c r="E2" s="71" t="n"/>
-      <c r="F2" s="71" t="n"/>
-      <c r="G2" s="71" t="n"/>
-      <c r="H2" s="71" t="n"/>
+      <c r="B2" s="91" t="n"/>
+      <c r="C2" s="91" t="n"/>
+      <c r="D2" s="91" t="n"/>
+      <c r="E2" s="91" t="n"/>
+      <c r="F2" s="91" t="n"/>
+      <c r="G2" s="91" t="n"/>
+      <c r="H2" s="92" t="n"/>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="73" t="inlineStr">
@@ -3196,13 +3295,13 @@
           <t>■ 今回の2大ゴール</t>
         </is>
       </c>
-      <c r="B3" s="71" t="n"/>
-      <c r="C3" s="71" t="n"/>
-      <c r="D3" s="71" t="n"/>
-      <c r="E3" s="71" t="n"/>
-      <c r="F3" s="71" t="n"/>
-      <c r="G3" s="71" t="n"/>
-      <c r="H3" s="71" t="n"/>
+      <c r="B3" s="91" t="n"/>
+      <c r="C3" s="91" t="n"/>
+      <c r="D3" s="91" t="n"/>
+      <c r="E3" s="91" t="n"/>
+      <c r="F3" s="91" t="n"/>
+      <c r="G3" s="91" t="n"/>
+      <c r="H3" s="92" t="n"/>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="74" t="inlineStr">
@@ -3211,18 +3310,18 @@
 （内定者同士・人事との最初の接点をつくり孤独感を解消）</t>
         </is>
       </c>
-      <c r="B4" s="71" t="n"/>
-      <c r="C4" s="71" t="n"/>
-      <c r="D4" s="71" t="n"/>
+      <c r="B4" s="91" t="n"/>
+      <c r="C4" s="91" t="n"/>
+      <c r="D4" s="92" t="n"/>
       <c r="E4" s="75" t="inlineStr">
         <is>
           <t>② 周りのネガティブな意見に自分なりの"回答ワード"を持って帰る
 （「派遣される側？」「建設業界？」→「業界NO.1」「本社勤め・選ぶ側」「安定した大手グループ」）</t>
         </is>
       </c>
-      <c r="F4" s="71" t="n"/>
-      <c r="G4" s="71" t="n"/>
-      <c r="H4" s="71" t="n"/>
+      <c r="F4" s="91" t="n"/>
+      <c r="G4" s="91" t="n"/>
+      <c r="H4" s="92" t="n"/>
     </row>
     <row r="5" ht="35" customHeight="1">
       <c r="A5" s="76" t="inlineStr">
@@ -3659,13 +3758,13 @@
           <t>■ グループ割り振り詳細</t>
         </is>
       </c>
-      <c r="B13" s="71" t="n"/>
-      <c r="C13" s="71" t="n"/>
-      <c r="D13" s="71" t="n"/>
-      <c r="E13" s="71" t="n"/>
-      <c r="F13" s="71" t="n"/>
-      <c r="G13" s="71" t="n"/>
-      <c r="H13" s="71" t="n"/>
+      <c r="B13" s="91" t="n"/>
+      <c r="C13" s="91" t="n"/>
+      <c r="D13" s="91" t="n"/>
+      <c r="E13" s="91" t="n"/>
+      <c r="F13" s="91" t="n"/>
+      <c r="G13" s="91" t="n"/>
+      <c r="H13" s="92" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="76" t="inlineStr">
@@ -3795,6 +3894,738 @@
       <c r="A17" s="73" t="inlineStr">
         <is>
           <t>■ 成功させるための5つのポイント</t>
+        </is>
+      </c>
+      <c r="B17" s="91" t="n"/>
+      <c r="C17" s="91" t="n"/>
+      <c r="D17" s="91" t="n"/>
+      <c r="E17" s="91" t="n"/>
+      <c r="F17" s="91" t="n"/>
+      <c r="G17" s="91" t="n"/>
+      <c r="H17" s="92" t="n"/>
+    </row>
+    <row r="18" ht="45" customHeight="1">
+      <c r="A18" s="80" t="inlineStr">
+        <is>
+          <t>✔ カメラON徹底</t>
+        </is>
+      </c>
+      <c r="B18" s="92" t="n"/>
+      <c r="C18" s="77" t="inlineStr">
+        <is>
+          <t>事前メールに「交流が目的なのでカメラONでご参加ください」と明記。当日冒頭でも笑顔でお願いする。強制感を出さず自然に促す。</t>
+        </is>
+      </c>
+      <c r="D18" s="91" t="n"/>
+      <c r="E18" s="91" t="n"/>
+      <c r="F18" s="91" t="n"/>
+      <c r="G18" s="91" t="n"/>
+      <c r="H18" s="92" t="n"/>
+    </row>
+    <row r="19" ht="45" customHeight="1">
+      <c r="A19" s="80" t="inlineStr">
+        <is>
+          <t>✔ 人事が一番楽しむ</t>
+        </is>
+      </c>
+      <c r="B19" s="92" t="n"/>
+      <c r="C19" s="77" t="inlineStr">
+        <is>
+          <t>人事担当者がテンション1.2倍・一番に自己開示することで「この会社楽しそう」という確信を植え付ける。「人事が楽しんでいる＝職場の雰囲気が良い」という無意識の推論を活用する。</t>
+        </is>
+      </c>
+      <c r="D19" s="91" t="n"/>
+      <c r="E19" s="91" t="n"/>
+      <c r="F19" s="91" t="n"/>
+      <c r="G19" s="91" t="n"/>
+      <c r="H19" s="92" t="n"/>
+    </row>
+    <row r="20" ht="45" customHeight="1">
+      <c r="A20" s="80" t="inlineStr">
+        <is>
+          <t>✔ リアクション推奨</t>
+        </is>
+      </c>
+      <c r="B20" s="92" t="n"/>
+      <c r="C20" s="77" t="inlineStr">
+        <is>
+          <t>拍手・ハートスタンプを積極的に使い、チャットを賑やかにする。冒頭で「スタンプ使い放題ですよ！」と促すことで一体感が生まれる。</t>
+        </is>
+      </c>
+      <c r="D20" s="91" t="n"/>
+      <c r="E20" s="91" t="n"/>
+      <c r="F20" s="91" t="n"/>
+      <c r="G20" s="91" t="n"/>
+      <c r="H20" s="92" t="n"/>
+    </row>
+    <row r="21" ht="45" customHeight="1">
+      <c r="A21" s="80" t="inlineStr">
+        <is>
+          <t>✔ 時間管理の徹底</t>
+        </is>
+      </c>
+      <c r="B21" s="92" t="n"/>
+      <c r="C21" s="77" t="inlineStr">
+        <is>
+          <t>各コンテンツに制限時間を設け、人事がタイムキーパーを兼務。削る優先順位：会社説明 &gt; 共通点探し &gt; ワーク②。クロージングは絶対に削らない。</t>
+        </is>
+      </c>
+      <c r="D21" s="91" t="n"/>
+      <c r="E21" s="91" t="n"/>
+      <c r="F21" s="91" t="n"/>
+      <c r="G21" s="91" t="n"/>
+      <c r="H21" s="92" t="n"/>
+    </row>
+    <row r="22" ht="45" customHeight="1">
+      <c r="A22" s="80" t="inlineStr">
+        <is>
+          <t>✔ ゴールを冒頭で共有</t>
+        </is>
+      </c>
+      <c r="B22" s="92" t="n"/>
+      <c r="C22" s="77" t="inlineStr">
+        <is>
+          <t>「今日のゴールは2つ」と冒頭で言うことで参加者の行動が変わる。ゴールを明確にしておくことでワーク②も「目的のある時間」として受け取られる。</t>
+        </is>
+      </c>
+      <c r="D22" s="91" t="n"/>
+      <c r="E22" s="91" t="n"/>
+      <c r="F22" s="91" t="n"/>
+      <c r="G22" s="91" t="n"/>
+      <c r="H22" s="92" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="17">
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C19:H19"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="E4:H4"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C22:H22"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="C18:H18"/>
+    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C21:H21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C20:H20"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="70" t="inlineStr">
+        <is>
+          <t>27新卒 内定承諾者向け 顔合わせ企画書（Zoom・60分）　【構成改訂版 v2】</t>
+        </is>
+      </c>
+      <c r="B1" s="71" t="n"/>
+      <c r="C1" s="71" t="n"/>
+      <c r="D1" s="71" t="n"/>
+      <c r="E1" s="71" t="n"/>
+      <c r="F1" s="71" t="n"/>
+      <c r="G1" s="71" t="n"/>
+      <c r="H1" s="71" t="n"/>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="72" t="inlineStr">
+        <is>
+          <t>参加者：内定承諾者 各グループ ＋ 人事担当　／　形式：Zoom　／　総時間：55〜60分</t>
+        </is>
+      </c>
+      <c r="B2" s="71" t="n"/>
+      <c r="C2" s="71" t="n"/>
+      <c r="D2" s="71" t="n"/>
+      <c r="E2" s="71" t="n"/>
+      <c r="F2" s="71" t="n"/>
+      <c r="G2" s="71" t="n"/>
+      <c r="H2" s="71" t="n"/>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="73" t="inlineStr">
+        <is>
+          <t>■ 今回の設計思想</t>
+        </is>
+      </c>
+      <c r="B3" s="71" t="n"/>
+      <c r="C3" s="71" t="n"/>
+      <c r="D3" s="71" t="n"/>
+      <c r="E3" s="71" t="n"/>
+      <c r="F3" s="71" t="n"/>
+      <c r="G3" s="71" t="n"/>
+      <c r="H3" s="71" t="n"/>
+    </row>
+    <row r="4" ht="80" customHeight="1">
+      <c r="A4" s="75" t="inlineStr">
+        <is>
+          <t>【最優先で避けること】会社説明を「考えさせるワーク」と組み合わせ、ネガティブな印象が残ったまま終了するリスク
+【構成の原則】
+アイスブレイク（自己紹介） → 楽しいワーク前半 → 休憩がてら会社説明（5分・インプットのみ） → 楽しいワーク後半 → クロージング
+会社説明は「アウトプットを求めない・5分・完結型」に徹する。
+ワーク後半は「盛り上がりが保証されており、時間通りに必ず完結できる」コンテンツを選定。不完全燃焼を構造上発生させない設計。</t>
+        </is>
+      </c>
+      <c r="B4" s="71" t="n"/>
+      <c r="C4" s="71" t="n"/>
+      <c r="D4" s="71" t="n"/>
+      <c r="E4" s="71" t="n"/>
+      <c r="F4" s="71" t="n"/>
+      <c r="G4" s="71" t="n"/>
+      <c r="H4" s="71" t="n"/>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="73" t="inlineStr">
+        <is>
+          <t>■ 全体タイムライン</t>
+        </is>
+      </c>
+      <c r="B5" s="71" t="n"/>
+      <c r="C5" s="71" t="n"/>
+      <c r="D5" s="71" t="n"/>
+      <c r="E5" s="71" t="n"/>
+      <c r="F5" s="71" t="n"/>
+      <c r="G5" s="71" t="n"/>
+      <c r="H5" s="71" t="n"/>
+    </row>
+    <row r="6" ht="50" customHeight="1">
+      <c r="A6" s="93" t="inlineStr">
+        <is>
+          <t>0〜5分
+流れ説明
++自己紹介</t>
+        </is>
+      </c>
+      <c r="B6" s="93" t="inlineStr">
+        <is>
+          <t>5〜15分
+アイスブレイク
+自己紹介リレー</t>
+        </is>
+      </c>
+      <c r="C6" s="94" t="inlineStr">
+        <is>
+          <t>15〜30分
+【ワーク前半】
+共通点探しバトル</t>
+        </is>
+      </c>
+      <c r="D6" s="95" t="inlineStr">
+        <is>
+          <t>30〜35分
+会社説明
+（休憩がてら）</t>
+        </is>
+      </c>
+      <c r="E6" s="96" t="inlineStr">
+        <is>
+          <t>35〜55分
+【ワーク後半】
+「実は私…」告白</t>
+        </is>
+      </c>
+      <c r="F6" s="97" t="inlineStr">
+        <is>
+          <t>55〜60分
+クロージング
+次回予告</t>
+        </is>
+      </c>
+      <c r="H6" s="71" t="n"/>
+    </row>
+    <row r="7" ht="5" customHeight="1">
+      <c r="A7" s="93" t="n"/>
+      <c r="B7" s="93" t="n"/>
+      <c r="C7" s="94" t="n"/>
+      <c r="D7" s="95" t="n"/>
+      <c r="E7" s="96" t="n"/>
+      <c r="F7" s="97" t="n"/>
+      <c r="H7" s="71" t="n"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="73" t="inlineStr">
+        <is>
+          <t>■ プログラム詳細</t>
+        </is>
+      </c>
+      <c r="B8" s="71" t="n"/>
+      <c r="C8" s="71" t="n"/>
+      <c r="D8" s="71" t="n"/>
+      <c r="E8" s="71" t="n"/>
+      <c r="F8" s="71" t="n"/>
+      <c r="G8" s="71" t="n"/>
+      <c r="H8" s="71" t="n"/>
+    </row>
+    <row r="9" ht="35" customHeight="1">
+      <c r="A9" s="76" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B9" s="76" t="inlineStr">
+        <is>
+          <t>コンテンツ名</t>
+        </is>
+      </c>
+      <c r="C9" s="76" t="inlineStr">
+        <is>
+          <t>時間
+（累計）</t>
+        </is>
+      </c>
+      <c r="D9" s="76" t="inlineStr">
+        <is>
+          <t>狙い（Why）</t>
+        </is>
+      </c>
+      <c r="E9" s="76" t="inlineStr">
+        <is>
+          <t>進行スクリプト（How）
+※かぎ括弧がそのまま使えるセリフ例</t>
+        </is>
+      </c>
+      <c r="F9" s="76" t="inlineStr">
+        <is>
+          <t>成功の判断基準</t>
+        </is>
+      </c>
+      <c r="G9" s="76" t="inlineStr">
+        <is>
+          <t>リスクと対策</t>
+        </is>
+      </c>
+      <c r="H9" s="76" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="130" customHeight="1">
+      <c r="A10" s="77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B10" s="98" t="inlineStr">
+        <is>
+          <t>入室待機
+・BGM</t>
+        </is>
+      </c>
+      <c r="C10" s="77" t="inlineStr">
+        <is>
+          <t>開始15分前
+（待機）</t>
+        </is>
+      </c>
+      <c r="D10" s="77" t="inlineStr">
+        <is>
+          <t>「この会社はちゃんとしている」という第一印象を開始前から形成する。緊張状態で入室する学生の不安を事前に下げる。</t>
+        </is>
+      </c>
+      <c r="E10" s="77" t="inlineStr">
+        <is>
+          <t>【準備チェックリスト】
+□ BGMを流す（Spotifyリラックス系推奨）
+□ 待機画面に「今日の流れ」スライドを表示
+□ チャットに「こんにちは！今日はよろしくお願いします😊 カメラONにしてもらえると嬉しいです！」を準備
+□ MC担当 / チャット＆タイム管理担当の役割確認
+【入室時の声かけ例】
+「〇〇さん、入ってくれましたね！今日はよろしくお願いします。全員揃うまで気楽にしていてください」</t>
+        </is>
+      </c>
+      <c r="F10" s="77" t="inlineStr">
+        <is>
+          <t>全員カメラON・笑顔で入室</t>
+        </is>
+      </c>
+      <c r="G10" s="77" t="inlineStr">
+        <is>
+          <t>無言入室が続く場合 → 個人名で「〇〇さん、今日どこから参加ですか？」と話しかける</t>
+        </is>
+      </c>
+      <c r="H10" s="77" t="inlineStr">
+        <is>
+          <t>開始5分前にリマインドをチャットで送る</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="130" customHeight="1">
+      <c r="A11" s="79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B11" s="99" t="inlineStr">
+        <is>
+          <t>流れ説明
+＋人事自己紹介</t>
+        </is>
+      </c>
+      <c r="C11" s="79" t="inlineStr">
+        <is>
+          <t>0〜5分
+（5分）</t>
+        </is>
+      </c>
+      <c r="D11" s="79" t="inlineStr">
+        <is>
+          <t>①ゴールを2つに絞って言語化することで参加者の心理的ハードルを下げる。②人事が先に自己開示することで「この場では自己開示してよい」という規範を示す（モデリング効果）。</t>
+        </is>
+      </c>
+      <c r="E11" s="79" t="inlineStr">
+        <is>
+          <t>【冒頭セリフ例（そのまま使用可）】
+「みなさん、こんにちは！今日は最初の顔合わせということでとても楽しみにしてきました。
+今日のゴールは2つだけ。①全員の顔と名前を覚える。②今日楽しかった、と思いながら画面を閉じる。それだけです！
+堅い時間にするつもりは全くないので、今日は楽しんでいってください。まず私から自己紹介しますね。」
+【人事自己紹介の構成（60秒）】
+① 名前・担当業務（10秒）
+② 今ハマっていること・推し（具体的に、20秒）
+③ 意外な一面・ギャップ（20秒）→ 後半ワークの布石にもなる
+④ 一言「今日は皆さんのこと知りたくてきました！」（10秒）</t>
+        </is>
+      </c>
+      <c r="F11" s="79" t="inlineStr">
+        <is>
+          <t>参加者が笑顔でうなずいている・チャットでリアクションがある</t>
+        </is>
+      </c>
+      <c r="G11" s="79" t="inlineStr">
+        <is>
+          <t>人事が緊張して棒読みになる → 必ず前日にリハーサルを実施する</t>
+        </is>
+      </c>
+      <c r="H11" s="79" t="inlineStr">
+        <is>
+          <t>スライド1枚：今日の流れ図を画面共有</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="130" customHeight="1">
+      <c r="A12" s="79" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B12" s="99" t="inlineStr">
+        <is>
+          <t>1分自己紹介
+リレー
+（アイスブレイク）</t>
+        </is>
+      </c>
+      <c r="C12" s="79" t="inlineStr">
+        <is>
+          <t>5〜15分
+（10分）</t>
+        </is>
+      </c>
+      <c r="D12" s="79" t="inlineStr">
+        <is>
+          <t>顔・名前・キャラクターを一致させる。「推し」は盛り上がりやすく自然な共感を生む。指名形式にすることで受動的参加を防ぎ全員が必ず1度発言する。</t>
+        </is>
+      </c>
+      <c r="E12" s="79" t="inlineStr">
+        <is>
+          <t>【項目（画面共有で表示）】
+① 名前・大学
+② 最近の推し or マイブーム（何でもOK）→ 可能なら画面に映す
+③ 一言キャッチフレーズ
+（例："見た目は地味ですが熱量だけはあります"）
+【進行セリフ例】
+「自己紹介をしていきます。推しは何でもOK！アイドルでも食べ物でも推し球団でも（笑）。最後に次の人を指名してバトンを渡してください。では〇〇さんからお願いします！」
+【チャット担当の動き（重要）】
+各発言にリアルタイムで反応を流す
+例：「〇〇大学！いいですね」「推し、わかります笑」
+→ スタンプ（拍手・ハート）を積極的に使う
+【参加者プロフィール活用ポイント（事前確認）】
+・富川（野球全国優勝）→「え、全国⁉」でチャットが沸く。早めに登場させたい
+・折笠（甲子園チア部優勝・学祭委員長80名）→ 発表慣れあり。場を引っ張ってくれる
+・本多（キックボクシング）→「え、格闘技⁉」で盛り上がる。なるべく前半に登場
+・佐々木（評価1位・録音→ロープレ繰り返し）→「努力の天才」キャラとして紹介できる</t>
+        </is>
+      </c>
+      <c r="F12" s="79" t="inlineStr">
+        <is>
+          <t>全員が1回は笑いを取れている・チャットが賑わっている</t>
+        </is>
+      </c>
+      <c r="G12" s="79" t="inlineStr">
+        <is>
+          <t>一人が長くなる → 「いいですね！じゃあ次の方にバトンを」と自然に促す</t>
+        </is>
+      </c>
+      <c r="H12" s="79" t="inlineStr">
+        <is>
+          <t>事前に推しが分かるものを画面に映すよう案内（メール or 当日冒頭）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="130" customHeight="1">
+      <c r="A13" s="81" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B13" s="89" t="inlineStr">
+        <is>
+          <t>【ワーク前半】
+共通点探し
+バトル</t>
+        </is>
+      </c>
+      <c r="C13" s="81" t="inlineStr">
+        <is>
+          <t>15〜30分
+（15分）</t>
+        </is>
+      </c>
+      <c r="D13" s="81" t="inlineStr">
+        <is>
+          <t>「意外な共通点」の発見は即座に親近感を生む（類似性の法則）。競争要素を加えることで自然な会話量が増え確実に盛り上がる。盛り上がった状態のまま会社説明へ橋渡しする。</t>
+        </is>
+      </c>
+      <c r="E13" s="81" t="inlineStr">
+        <is>
+          <t>【ルール（画面共有で表示）】
+① 15分間でできるだけ多くの共通点を見つける
+② 当たり前すぎる共通点は禁止（大学生・服を着ている 等）
+③ 深い共通点ほど高得点（"日本人" &lt; "小学校で習い事を途中で辞めた経験あり"）
+【進行セリフ例】
+「次は共通点探しゲームです！15分間でできるだけ多くの共通点を見つけてください。自己紹介で話したこと以外でOK。趣味・好きな食べ物・苦手なこと・子どもの頃の話など何でも。"当たり前すぎる禁止"なので"全員大学生"はナシです（笑）。じゃあスタート！」
+【14分経過時の声かけ】
+「あと1分！最後の一個、面白いやつ絞り出して！」
+【発表（2〜3分）】
+「各チームから！特に面白いやつ優先でどうぞ！」
+→ 人事が1〜2個深掘りして温める
+【会社説明への橋渡しセリフ（重要）】
+「いや〜、思った以上に共通点ありましたね！さてここで少しだけ脳を休めて、弊社のことを改めて3分でご紹介させてください。"少しだけ"なので安心してください（笑）」</t>
+        </is>
+      </c>
+      <c r="F13" s="81" t="inlineStr">
+        <is>
+          <t>各グループ10個以上の共通点・笑いが起きている・拍手スタンプが飛び交っている</t>
+        </is>
+      </c>
+      <c r="G13" s="81" t="inlineStr">
+        <is>
+          <t>会話が停滞した場合 → 人事から「犬派・猫派どっち？」「朝型・夜型？」などお題を投下</t>
+        </is>
+      </c>
+      <c r="H13" s="81" t="inlineStr">
+        <is>
+          <t>6/23（女子4名）は深掘りの質重視。6/30（混合6名）は数を競う形式で盛り上げる</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="130" customHeight="1">
+      <c r="A14" s="85" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B14" s="100" t="inlineStr">
+        <is>
+          <t>会社説明
+（休憩がてら
+インプットのみ）</t>
+        </is>
+      </c>
+      <c r="C14" s="85" t="inlineStr">
+        <is>
+          <t>30〜35分
+（5分）</t>
+        </is>
+      </c>
+      <c r="D14" s="85" t="inlineStr">
+        <is>
+          <t>盛り上がったワーク前半の直後に「自然な休憩」として差し込む。アウトプットは一切求めない。3つのキーワードを記憶に残すだけでよい。「ネガティブ払拭を目的にしている」と悟られないよう、ポジティブな情報として自然に届ける。</t>
+        </is>
+      </c>
+      <c r="E14" s="85" t="inlineStr">
+        <is>
+          <t>【冒頭セリフ（警戒させないための言い回し）】
+「少しだけ弊社のことをお伝えさせてください。まだあまり知らない状態で入社するのも不安だと思うので、改めて簡単にご紹介します。3分だけお付き合いください！」
+【伝える3点（各1分・計3分）】
+①業界NO.1の安定性
+「人材派遣業界の中でも建設・インフラ特化で業界シェアトップクラスです。建設インフラは社会インフラそのものなので景気に左右されにくい特性があります。」
+②本社勤め・選ぶ側
+「皆さんは派遣される側ではなく、派遣する側・コーディネートする側です。毎日スーツで本社出社が基本で、現場仕事ではありません。」
+③大手グループの安定感
+「〇〇グループ傘下として、バックアップ体制もしっかりしています。」
+【締めセリフ（次のワークへのつなぎ）】
+「友達や親御さんに"どんな会社？"と聞かれたときこの3つを話すだけで説明になります。覚えておいてくださいね。じゃあ後半戦いきましょうか！後半の方が絶対盛り上がる予感がしているので（笑）」</t>
+        </is>
+      </c>
+      <c r="F14" s="85" t="inlineStr">
+        <is>
+          <t>ネガティブな反応が出ていない・参加者がうなずいている</t>
+        </is>
+      </c>
+      <c r="G14" s="85" t="inlineStr">
+        <is>
+          <t>説明が長くなる → 必ず5分で切る。詳細は後日メールで補足
+暗い雰囲気になる → 締めセリフで「後半戦」への期待感を高めることで切り替える</t>
+        </is>
+      </c>
+      <c r="H14" s="85" t="inlineStr">
+        <is>
+          <t>説明会資料から該当スライドを最大3枚に絞る。資料を見せすぎない</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="130" customHeight="1">
+      <c r="A15" s="101" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B15" s="102" t="inlineStr">
+        <is>
+          <t>【ワーク後半】
+「実は私…」
+ギャップ告白</t>
+        </is>
+      </c>
+      <c r="C15" s="101" t="inlineStr">
+        <is>
+          <t>35〜55分
+（20分）</t>
+        </is>
+      </c>
+      <c r="D15" s="101" t="inlineStr">
+        <is>
+          <t>「完璧に見せようとしない・少しの隙を見せ合う」ことで心理的安全性が一気に高まる（自己開示の返報性）。笑いと「この人も普通だな」という親近感が同時に生まれる。1人1〜2分の発表形式のため時間管理が容易で、不完全燃焼が構造上起きない設計。</t>
+        </is>
+      </c>
+      <c r="E15" s="101" t="inlineStr">
+        <is>
+          <t>【お題（画面共有で表示）】
+「こう見えて、実は〇〇なんです」
+【例（表示しておくと発言しやすくなる）】
+・こう見えて、実はシェフ並みに料理ができます
+・こう見えて、実はホラーが大の苦手です
+・こう見えて、実は毎朝5時に起きています
+・こう見えて、実は推しのために年10万円以上使っています
+【進行セリフ例】
+「後半戦いきましょう！テーマはこれです。"こう見えて、実は〇〇"。外見とのギャップ、意外な趣味、誰も知らない一面、なんでもOKです。恥ずかしい話ほど盛り上がるので（笑）。まず私からいきますね！」
+【人事の自己開示（必ず最初に言う）】
+「こう見えて実は、〇〇（具体的で少し恥ずかしいこと）なんです」
+→ 人事が先に少し恥ずかしい話をすることで場の安全性が一気に上がる
+【順番の目安】
+人事 → 自己紹介で最も盛り上がっていた人 → リレー形式で全員
+【チャット担当の動き】
+発言のたびに「え！？」「笑」「それわかる」「知らなかった！」を流す
+→ スタンプ連打を促す
+【ひと工夫：ギャップ大賞で締める（残り5分）】
+「一番意外だったギャップ大賞」をZoomの挙手機能や投票で決める
+→ 受賞者に一言コメントをもらい笑いで締める</t>
+        </is>
+      </c>
+      <c r="F15" s="101" t="inlineStr">
+        <is>
+          <t>全員が発表できている・笑いが複数回起きている・「大賞」発表で盛り上がっている</t>
+        </is>
+      </c>
+      <c r="G15" s="101" t="inlineStr">
+        <is>
+          <t>誰も口火を切れない → 人事が最初に自己開示することで解消（必須）
+時間が余る → 「大賞の理由を聞く」「人事が2回目を語る」で自然に埋まる
+時間が足りなくなる → 大賞投票を省略して全員発表を優先</t>
+        </is>
+      </c>
+      <c r="H15" s="101" t="inlineStr">
+        <is>
+          <t>6/23（女子4名）は深掘りしやすいため1人2分可。6/30（混合6名）は1人90秒を目安に</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="130" customHeight="1">
+      <c r="A16" s="103" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B16" s="104" t="inlineStr">
+        <is>
+          <t>クロージング
+＋次回予告</t>
+        </is>
+      </c>
+      <c r="C16" s="103" t="inlineStr">
+        <is>
+          <t>55〜60分
+（5分）</t>
+        </is>
+      </c>
+      <c r="D16" s="103" t="inlineStr">
+        <is>
+          <t>「またこのメンバーに会いたい」という感情で終わらせる。次のイベントへの期待値を上げ入社までの緩やかなつながりを維持する。アンケートで本音を収集し次回以降に活かす。</t>
+        </is>
+      </c>
+      <c r="E16" s="103" t="inlineStr">
+        <is>
+          <t>【締めセリフ例（そのまま使用可）】
+「今日はありがとうございました！正直、最初はどんな会話になるか少し緊張していたんですが、みなさんのおかげでとても盛り上がりましたね。
+今日だけで〇〇さんが実はシェフ並みに料理できるとか（笑）、△△さんが毎朝5時起きとか、一気に仲間感が出た気がしています。
+次は〇月〇日に対面での顔合わせを予定しています。今度は直接会えるのが楽しみです！それまでも何かあれば遠慮なく私に連絡してください。連絡先はチャットに貼りますね。
+では最後にアンケートだけお願いします。1分で終わります！URLをチャットに貼ります。」
+【チャットに貼るもの（事前にコピー準備）】
+□ アンケートフォームURL
+□ 次回日程（テキスト）
+□ 人事担当の連絡先（LINE or メール）
+【アンケート項目（5問・1分以内）】
+① 今日の満足度（5段階）
+② 一番楽しかったコンテンツ（選択式）
+③ 入社に対して不安に思っていることがあれば（自由記述・任意）
+④ 次回も参加したいと思えましたか（Yes/No）
+⑤ 一言感想（任意）</t>
+        </is>
+      </c>
+      <c r="F16" s="103" t="inlineStr">
+        <is>
+          <t>参加者全員がアンケートを送信・次回日程をスケジュール登録</t>
+        </is>
+      </c>
+      <c r="G16" s="103" t="inlineStr">
+        <is>
+          <t>時間オーバーの場合 → ワーク後半の「大賞投票」を省略する。クロージング時間は絶対に削らない</t>
+        </is>
+      </c>
+      <c r="H16" s="103" t="inlineStr">
+        <is>
+          <t>クロージング後に5〜10分の任意雑談タイムを設けると帰属意識が上がる</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="73" t="inlineStr">
+        <is>
+          <t>■ グループ割り振り詳細</t>
         </is>
       </c>
       <c r="B17" s="71" t="n"/>
@@ -3805,88 +4636,152 @@
       <c r="G17" s="71" t="n"/>
       <c r="H17" s="71" t="n"/>
     </row>
-    <row r="18" ht="45" customHeight="1">
-      <c r="A18" s="80" t="inlineStr">
-        <is>
-          <t>✔ カメラON徹底</t>
-        </is>
-      </c>
-      <c r="B18" s="71" t="n"/>
-      <c r="C18" s="77" t="inlineStr">
-        <is>
-          <t>事前メールに「交流が目的なのでカメラONでご参加ください」と明記。当日冒頭でも笑顔でお願いする。強制感を出さず自然に促す。</t>
-        </is>
-      </c>
-      <c r="D18" s="71" t="n"/>
-      <c r="E18" s="71" t="n"/>
-      <c r="F18" s="71" t="n"/>
-      <c r="G18" s="71" t="n"/>
-      <c r="H18" s="71" t="n"/>
-    </row>
-    <row r="19" ht="45" customHeight="1">
-      <c r="A19" s="80" t="inlineStr">
-        <is>
-          <t>✔ 人事が一番楽しむ</t>
-        </is>
-      </c>
-      <c r="B19" s="71" t="n"/>
-      <c r="C19" s="77" t="inlineStr">
-        <is>
-          <t>人事担当者がテンション1.2倍・一番に自己開示することで「この会社楽しそう」という確信を植え付ける。「人事が楽しんでいる＝職場の雰囲気が良い」という無意識の推論を活用する。</t>
-        </is>
-      </c>
-      <c r="D19" s="71" t="n"/>
-      <c r="E19" s="71" t="n"/>
-      <c r="F19" s="71" t="n"/>
-      <c r="G19" s="71" t="n"/>
-      <c r="H19" s="71" t="n"/>
-    </row>
-    <row r="20" ht="45" customHeight="1">
-      <c r="A20" s="80" t="inlineStr">
-        <is>
-          <t>✔ リアクション推奨</t>
-        </is>
-      </c>
-      <c r="B20" s="71" t="n"/>
-      <c r="C20" s="77" t="inlineStr">
-        <is>
-          <t>拍手・ハートスタンプを積極的に使い、チャットを賑やかにする。冒頭で「スタンプ使い放題ですよ！」と促すことで一体感が生まれる。</t>
-        </is>
-      </c>
-      <c r="D20" s="71" t="n"/>
-      <c r="E20" s="71" t="n"/>
-      <c r="F20" s="71" t="n"/>
-      <c r="G20" s="71" t="n"/>
-      <c r="H20" s="71" t="n"/>
-    </row>
-    <row r="21" ht="45" customHeight="1">
-      <c r="A21" s="80" t="inlineStr">
-        <is>
-          <t>✔ 時間管理の徹底</t>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="76" t="inlineStr">
+        <is>
+          <t>日程</t>
+        </is>
+      </c>
+      <c r="B18" s="76" t="inlineStr">
+        <is>
+          <t>規模・構成</t>
+        </is>
+      </c>
+      <c r="C18" s="76" t="inlineStr">
+        <is>
+          <t>参加者</t>
+        </is>
+      </c>
+      <c r="D18" s="76" t="inlineStr">
+        <is>
+          <t>各自キャラクター活用ポイント</t>
+        </is>
+      </c>
+      <c r="E18" s="76" t="inlineStr">
+        <is>
+          <t>担当人事</t>
+        </is>
+      </c>
+      <c r="F18" s="76" t="inlineStr">
+        <is>
+          <t>特記事項</t>
+        </is>
+      </c>
+      <c r="G18" s="76" t="inlineStr"/>
+      <c r="H18" s="76" t="inlineStr"/>
+    </row>
+    <row r="19" ht="85" customHeight="1">
+      <c r="A19" s="89" t="inlineStr">
+        <is>
+          <t>2026/6/23
+11:00〜12:00</t>
+        </is>
+      </c>
+      <c r="B19" s="81" t="inlineStr">
+        <is>
+          <t>4名
+女性のみ</t>
+        </is>
+      </c>
+      <c r="C19" s="81" t="inlineStr">
+        <is>
+          <t>市川 結菜（神奈川大学）
+柳澤 明（東京経済大学）
+荒井 翠（駒澤大学）
+根本 彩花（東京富士大学）</t>
+        </is>
+      </c>
+      <c r="D19" s="81" t="inlineStr">
+        <is>
+          <t>【市川】企業研究済・まとめ役 → 自己紹介リレーで指名役を任せると流れが整う
+【荒井】心理学・ホスピタリティ高め → 共通点探しで他者への質問が得意
+【根本】肝が据わっている → ギャップ告白で意外な発言をしてくれる可能性大
+【柳澤】天真爛漫 → 場を温める存在</t>
+        </is>
+      </c>
+      <c r="E19" s="81" t="inlineStr">
+        <is>
+          <t>齋藤（MC）
+もう1名（チャット管理）</t>
+        </is>
+      </c>
+      <c r="F19" s="81" t="inlineStr">
+        <is>
+          <t>少人数のため深掘りしやすい。共通点の"質"重視。ギャップ告白は1人2分取れる。</t>
+        </is>
+      </c>
+      <c r="G19" s="81" t="inlineStr"/>
+      <c r="H19" s="81" t="inlineStr"/>
+    </row>
+    <row r="20" ht="85" customHeight="1">
+      <c r="A20" s="90" t="inlineStr">
+        <is>
+          <t>2026/6/30
+15:00〜16:00</t>
+        </is>
+      </c>
+      <c r="B20" s="83" t="inlineStr">
+        <is>
+          <t>6名
+女3・男3</t>
+        </is>
+      </c>
+      <c r="C20" s="83" t="inlineStr">
+        <is>
+          <t>富川 哲太（大阪経済大学）
+西山 心町（東海大学）
+吉田 雅野（大東文化大学）
+折笠 未來美（仙台白百合女子大学）
+佐々木 七都（福岡大学）
+本多 諒（九州産業大学）</t>
+        </is>
+      </c>
+      <c r="D20" s="83" t="inlineStr">
+        <is>
+          <t>【富川】野球全国優勝・全寮制 → 自己紹介リレーで早めに登場させる。「え、全国⁉」で場が沸く
+【折笠】甲子園チア部優勝・学祭委員長80名 → 発表慣れあり。場を引っ張ってくれる
+【本多】ボクサー → ギャップ告白で最大の笑いが取れる。後半の一番手候補
+【佐々木】評価1位・録音→ロープレ繰り返し → 「努力の鬼」キャラで紹介すると共感を集める</t>
+        </is>
+      </c>
+      <c r="E20" s="83" t="inlineStr">
+        <is>
+          <t>齋藤（MC）
+もう1名（チャット管理）</t>
+        </is>
+      </c>
+      <c r="F20" s="83" t="inlineStr">
+        <is>
+          <t>男女混合で自然と盛り上がりやすい。共通点の"数"を競う形式。ギャップ告白は1人90秒目安。</t>
+        </is>
+      </c>
+      <c r="G20" s="83" t="inlineStr"/>
+      <c r="H20" s="83" t="inlineStr"/>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="73" t="inlineStr">
+        <is>
+          <t>■ 成功させるための5つのポイント</t>
         </is>
       </c>
       <c r="B21" s="71" t="n"/>
-      <c r="C21" s="77" t="inlineStr">
-        <is>
-          <t>各コンテンツに制限時間を設け、人事がタイムキーパーを兼務。削る優先順位：会社説明 &gt; 共通点探し &gt; ワーク②。クロージングは絶対に削らない。</t>
-        </is>
-      </c>
+      <c r="C21" s="71" t="n"/>
       <c r="D21" s="71" t="n"/>
       <c r="E21" s="71" t="n"/>
       <c r="F21" s="71" t="n"/>
       <c r="G21" s="71" t="n"/>
       <c r="H21" s="71" t="n"/>
     </row>
-    <row r="22" ht="45" customHeight="1">
+    <row r="22" ht="42" customHeight="1">
       <c r="A22" s="80" t="inlineStr">
         <is>
-          <t>✔ ゴールを冒頭で共有</t>
+          <t>✔ カメラON徹底</t>
         </is>
       </c>
       <c r="B22" s="71" t="n"/>
       <c r="C22" s="77" t="inlineStr">
         <is>
-          <t>「今日のゴールは2つ」と冒頭で言うことで参加者の行動が変わる。ゴールを明確にしておくことでワーク②も「目的のある時間」として受け取られる。</t>
+          <t>事前メールに「交流が目的なのでカメラONでご参加ください」と明記。当日冒頭でも笑顔でお願いする。強制感を出さず自然に促す。</t>
         </is>
       </c>
       <c r="D22" s="71" t="n"/>
@@ -3895,23 +4790,96 @@
       <c r="G22" s="71" t="n"/>
       <c r="H22" s="71" t="n"/>
     </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="80" t="inlineStr">
+        <is>
+          <t>✔ 人事が一番楽しむ</t>
+        </is>
+      </c>
+      <c r="B23" s="71" t="n"/>
+      <c r="C23" s="77" t="inlineStr">
+        <is>
+          <t>人事担当者がテンション1.2倍・一番に自己開示することで「この会社楽しそう」という確信を植え付ける。ギャップ告白では人事が最初に"少し恥ずかしい話"をすることが必須。</t>
+        </is>
+      </c>
+      <c r="D23" s="71" t="n"/>
+      <c r="E23" s="71" t="n"/>
+      <c r="F23" s="71" t="n"/>
+      <c r="G23" s="71" t="n"/>
+      <c r="H23" s="71" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="80" t="inlineStr">
+        <is>
+          <t>✔ リアクション推奨</t>
+        </is>
+      </c>
+      <c r="B24" s="71" t="n"/>
+      <c r="C24" s="77" t="inlineStr">
+        <is>
+          <t>拍手・ハートスタンプを積極的に使い、チャットを賑やかにする。冒頭で「スタンプ使い放題ですよ！」と促すことで一体感が生まれる。</t>
+        </is>
+      </c>
+      <c r="D24" s="71" t="n"/>
+      <c r="E24" s="71" t="n"/>
+      <c r="F24" s="71" t="n"/>
+      <c r="G24" s="71" t="n"/>
+      <c r="H24" s="71" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="80" t="inlineStr">
+        <is>
+          <t>✔ 時間管理の徹底</t>
+        </is>
+      </c>
+      <c r="B25" s="71" t="n"/>
+      <c r="C25" s="77" t="inlineStr">
+        <is>
+          <t>削る優先順位：大賞投票 &gt; 共通点発表の深掘り &gt; 会社説明の一部。クロージングとギャップ告白（全員発表）は絶対に削らない。</t>
+        </is>
+      </c>
+      <c r="D25" s="71" t="n"/>
+      <c r="E25" s="71" t="n"/>
+      <c r="F25" s="71" t="n"/>
+      <c r="G25" s="71" t="n"/>
+      <c r="H25" s="71" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="80" t="inlineStr">
+        <is>
+          <t>✔ 会社説明は橋渡しに徹する</t>
+        </is>
+      </c>
+      <c r="B26" s="71" t="n"/>
+      <c r="C26" s="77" t="inlineStr">
+        <is>
+          <t>会社説明はインプットだけで完結させる。発言・考える・発表を一切求めない。5分を厳守し、最後は「後半戦への期待感」で締めることで雰囲気を維持する。</t>
+        </is>
+      </c>
+      <c r="D26" s="71" t="n"/>
+      <c r="E26" s="71" t="n"/>
+      <c r="F26" s="71" t="n"/>
+      <c r="G26" s="71" t="n"/>
+      <c r="H26" s="71" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="C20:H20"/>
-    <mergeCell ref="A20:B20"/>
+  <mergeCells count="18">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="C25:H25"/>
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="C19:H19"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:H24"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C26:H26"/>
+    <mergeCell ref="C22:H22"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="E4:H4"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C22:H22"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="C18:H18"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C21:H21"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C23:H23"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A8:H8"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="A17:H17"/>
   </mergeCells>

--- a/6月顔合わせ企画書_改善版.xlsx
+++ b/6月顔合わせ企画書_改善版.xlsx
@@ -13,6 +13,7 @@
     <sheet name="目的" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="【改善版】6月顔合わせ企画書" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="【改善版v2】6月企画書" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="【改善版v3】6月企画書" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191028" fullCalcOnLoad="1"/>
@@ -22,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="32">
+  <fonts count="34">
     <font>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
@@ -238,8 +239,18 @@
       <b val="1"/>
       <sz val="8"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00375623"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00375623"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -310,6 +321,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D9EAD3"/>
         <bgColor rgb="00D9EAD3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -685,7 +702,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="105">
+  <cellXfs count="107">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -911,6 +928,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="12" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="13" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3996,6 +4019,7 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A1:H1"/>
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A21:B21"/>
@@ -4007,12 +4031,11 @@
     <mergeCell ref="C22:H22"/>
     <mergeCell ref="A13:H13"/>
     <mergeCell ref="C18:H18"/>
-    <mergeCell ref="A17:H17"/>
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="C20:H20"/>
     <mergeCell ref="A18:B18"/>
     <mergeCell ref="C21:H21"/>
     <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C20:H20"/>
+    <mergeCell ref="A17:H17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4043,13 +4066,13 @@
           <t>27新卒 内定承諾者向け 顔合わせ企画書（Zoom・60分）　【構成改訂版 v2】</t>
         </is>
       </c>
-      <c r="B1" s="71" t="n"/>
-      <c r="C1" s="71" t="n"/>
-      <c r="D1" s="71" t="n"/>
-      <c r="E1" s="71" t="n"/>
-      <c r="F1" s="71" t="n"/>
-      <c r="G1" s="71" t="n"/>
-      <c r="H1" s="71" t="n"/>
+      <c r="B1" s="91" t="n"/>
+      <c r="C1" s="91" t="n"/>
+      <c r="D1" s="91" t="n"/>
+      <c r="E1" s="91" t="n"/>
+      <c r="F1" s="91" t="n"/>
+      <c r="G1" s="91" t="n"/>
+      <c r="H1" s="92" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="72" t="inlineStr">
@@ -4057,13 +4080,13 @@
           <t>参加者：内定承諾者 各グループ ＋ 人事担当　／　形式：Zoom　／　総時間：55〜60分</t>
         </is>
       </c>
-      <c r="B2" s="71" t="n"/>
-      <c r="C2" s="71" t="n"/>
-      <c r="D2" s="71" t="n"/>
-      <c r="E2" s="71" t="n"/>
-      <c r="F2" s="71" t="n"/>
-      <c r="G2" s="71" t="n"/>
-      <c r="H2" s="71" t="n"/>
+      <c r="B2" s="91" t="n"/>
+      <c r="C2" s="91" t="n"/>
+      <c r="D2" s="91" t="n"/>
+      <c r="E2" s="91" t="n"/>
+      <c r="F2" s="91" t="n"/>
+      <c r="G2" s="91" t="n"/>
+      <c r="H2" s="92" t="n"/>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="73" t="inlineStr">
@@ -4071,13 +4094,13 @@
           <t>■ 今回の設計思想</t>
         </is>
       </c>
-      <c r="B3" s="71" t="n"/>
-      <c r="C3" s="71" t="n"/>
-      <c r="D3" s="71" t="n"/>
-      <c r="E3" s="71" t="n"/>
-      <c r="F3" s="71" t="n"/>
-      <c r="G3" s="71" t="n"/>
-      <c r="H3" s="71" t="n"/>
+      <c r="B3" s="91" t="n"/>
+      <c r="C3" s="91" t="n"/>
+      <c r="D3" s="91" t="n"/>
+      <c r="E3" s="91" t="n"/>
+      <c r="F3" s="91" t="n"/>
+      <c r="G3" s="91" t="n"/>
+      <c r="H3" s="92" t="n"/>
     </row>
     <row r="4" ht="80" customHeight="1">
       <c r="A4" s="75" t="inlineStr">
@@ -4089,13 +4112,13 @@
 ワーク後半は「盛り上がりが保証されており、時間通りに必ず完結できる」コンテンツを選定。不完全燃焼を構造上発生させない設計。</t>
         </is>
       </c>
-      <c r="B4" s="71" t="n"/>
-      <c r="C4" s="71" t="n"/>
-      <c r="D4" s="71" t="n"/>
-      <c r="E4" s="71" t="n"/>
-      <c r="F4" s="71" t="n"/>
-      <c r="G4" s="71" t="n"/>
-      <c r="H4" s="71" t="n"/>
+      <c r="B4" s="91" t="n"/>
+      <c r="C4" s="91" t="n"/>
+      <c r="D4" s="91" t="n"/>
+      <c r="E4" s="91" t="n"/>
+      <c r="F4" s="91" t="n"/>
+      <c r="G4" s="91" t="n"/>
+      <c r="H4" s="92" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="73" t="inlineStr">
@@ -4103,13 +4126,13 @@
           <t>■ 全体タイムライン</t>
         </is>
       </c>
-      <c r="B5" s="71" t="n"/>
-      <c r="C5" s="71" t="n"/>
-      <c r="D5" s="71" t="n"/>
-      <c r="E5" s="71" t="n"/>
-      <c r="F5" s="71" t="n"/>
-      <c r="G5" s="71" t="n"/>
-      <c r="H5" s="71" t="n"/>
+      <c r="B5" s="91" t="n"/>
+      <c r="C5" s="91" t="n"/>
+      <c r="D5" s="91" t="n"/>
+      <c r="E5" s="91" t="n"/>
+      <c r="F5" s="91" t="n"/>
+      <c r="G5" s="91" t="n"/>
+      <c r="H5" s="92" t="n"/>
     </row>
     <row r="6" ht="50" customHeight="1">
       <c r="A6" s="93" t="inlineStr">
@@ -4171,13 +4194,13 @@
           <t>■ プログラム詳細</t>
         </is>
       </c>
-      <c r="B8" s="71" t="n"/>
-      <c r="C8" s="71" t="n"/>
-      <c r="D8" s="71" t="n"/>
-      <c r="E8" s="71" t="n"/>
-      <c r="F8" s="71" t="n"/>
-      <c r="G8" s="71" t="n"/>
-      <c r="H8" s="71" t="n"/>
+      <c r="B8" s="91" t="n"/>
+      <c r="C8" s="91" t="n"/>
+      <c r="D8" s="91" t="n"/>
+      <c r="E8" s="91" t="n"/>
+      <c r="F8" s="91" t="n"/>
+      <c r="G8" s="91" t="n"/>
+      <c r="H8" s="92" t="n"/>
     </row>
     <row r="9" ht="35" customHeight="1">
       <c r="A9" s="76" t="inlineStr">
@@ -4628,13 +4651,13 @@
           <t>■ グループ割り振り詳細</t>
         </is>
       </c>
-      <c r="B17" s="71" t="n"/>
-      <c r="C17" s="71" t="n"/>
-      <c r="D17" s="71" t="n"/>
-      <c r="E17" s="71" t="n"/>
-      <c r="F17" s="71" t="n"/>
-      <c r="G17" s="71" t="n"/>
-      <c r="H17" s="71" t="n"/>
+      <c r="B17" s="91" t="n"/>
+      <c r="C17" s="91" t="n"/>
+      <c r="D17" s="91" t="n"/>
+      <c r="E17" s="91" t="n"/>
+      <c r="F17" s="91" t="n"/>
+      <c r="G17" s="91" t="n"/>
+      <c r="H17" s="92" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="76" t="inlineStr">
@@ -4764,13 +4787,13 @@
           <t>■ 成功させるための5つのポイント</t>
         </is>
       </c>
-      <c r="B21" s="71" t="n"/>
-      <c r="C21" s="71" t="n"/>
-      <c r="D21" s="71" t="n"/>
-      <c r="E21" s="71" t="n"/>
-      <c r="F21" s="71" t="n"/>
-      <c r="G21" s="71" t="n"/>
-      <c r="H21" s="71" t="n"/>
+      <c r="B21" s="91" t="n"/>
+      <c r="C21" s="91" t="n"/>
+      <c r="D21" s="91" t="n"/>
+      <c r="E21" s="91" t="n"/>
+      <c r="F21" s="91" t="n"/>
+      <c r="G21" s="91" t="n"/>
+      <c r="H21" s="92" t="n"/>
     </row>
     <row r="22" ht="42" customHeight="1">
       <c r="A22" s="80" t="inlineStr">
@@ -4778,17 +4801,17 @@
           <t>✔ カメラON徹底</t>
         </is>
       </c>
-      <c r="B22" s="71" t="n"/>
+      <c r="B22" s="92" t="n"/>
       <c r="C22" s="77" t="inlineStr">
         <is>
           <t>事前メールに「交流が目的なのでカメラONでご参加ください」と明記。当日冒頭でも笑顔でお願いする。強制感を出さず自然に促す。</t>
         </is>
       </c>
-      <c r="D22" s="71" t="n"/>
-      <c r="E22" s="71" t="n"/>
-      <c r="F22" s="71" t="n"/>
-      <c r="G22" s="71" t="n"/>
-      <c r="H22" s="71" t="n"/>
+      <c r="D22" s="91" t="n"/>
+      <c r="E22" s="91" t="n"/>
+      <c r="F22" s="91" t="n"/>
+      <c r="G22" s="91" t="n"/>
+      <c r="H22" s="92" t="n"/>
     </row>
     <row r="23" ht="42" customHeight="1">
       <c r="A23" s="80" t="inlineStr">
@@ -4796,17 +4819,17 @@
           <t>✔ 人事が一番楽しむ</t>
         </is>
       </c>
-      <c r="B23" s="71" t="n"/>
+      <c r="B23" s="92" t="n"/>
       <c r="C23" s="77" t="inlineStr">
         <is>
           <t>人事担当者がテンション1.2倍・一番に自己開示することで「この会社楽しそう」という確信を植え付ける。ギャップ告白では人事が最初に"少し恥ずかしい話"をすることが必須。</t>
         </is>
       </c>
-      <c r="D23" s="71" t="n"/>
-      <c r="E23" s="71" t="n"/>
-      <c r="F23" s="71" t="n"/>
-      <c r="G23" s="71" t="n"/>
-      <c r="H23" s="71" t="n"/>
+      <c r="D23" s="91" t="n"/>
+      <c r="E23" s="91" t="n"/>
+      <c r="F23" s="91" t="n"/>
+      <c r="G23" s="91" t="n"/>
+      <c r="H23" s="92" t="n"/>
     </row>
     <row r="24" ht="42" customHeight="1">
       <c r="A24" s="80" t="inlineStr">
@@ -4814,17 +4837,17 @@
           <t>✔ リアクション推奨</t>
         </is>
       </c>
-      <c r="B24" s="71" t="n"/>
+      <c r="B24" s="92" t="n"/>
       <c r="C24" s="77" t="inlineStr">
         <is>
           <t>拍手・ハートスタンプを積極的に使い、チャットを賑やかにする。冒頭で「スタンプ使い放題ですよ！」と促すことで一体感が生まれる。</t>
         </is>
       </c>
-      <c r="D24" s="71" t="n"/>
-      <c r="E24" s="71" t="n"/>
-      <c r="F24" s="71" t="n"/>
-      <c r="G24" s="71" t="n"/>
-      <c r="H24" s="71" t="n"/>
+      <c r="D24" s="91" t="n"/>
+      <c r="E24" s="91" t="n"/>
+      <c r="F24" s="91" t="n"/>
+      <c r="G24" s="91" t="n"/>
+      <c r="H24" s="92" t="n"/>
     </row>
     <row r="25" ht="42" customHeight="1">
       <c r="A25" s="80" t="inlineStr">
@@ -4832,17 +4855,17 @@
           <t>✔ 時間管理の徹底</t>
         </is>
       </c>
-      <c r="B25" s="71" t="n"/>
+      <c r="B25" s="92" t="n"/>
       <c r="C25" s="77" t="inlineStr">
         <is>
           <t>削る優先順位：大賞投票 &gt; 共通点発表の深掘り &gt; 会社説明の一部。クロージングとギャップ告白（全員発表）は絶対に削らない。</t>
         </is>
       </c>
-      <c r="D25" s="71" t="n"/>
-      <c r="E25" s="71" t="n"/>
-      <c r="F25" s="71" t="n"/>
-      <c r="G25" s="71" t="n"/>
-      <c r="H25" s="71" t="n"/>
+      <c r="D25" s="91" t="n"/>
+      <c r="E25" s="91" t="n"/>
+      <c r="F25" s="91" t="n"/>
+      <c r="G25" s="91" t="n"/>
+      <c r="H25" s="92" t="n"/>
     </row>
     <row r="26" ht="42" customHeight="1">
       <c r="A26" s="80" t="inlineStr">
@@ -4850,17 +4873,17 @@
           <t>✔ 会社説明は橋渡しに徹する</t>
         </is>
       </c>
-      <c r="B26" s="71" t="n"/>
+      <c r="B26" s="92" t="n"/>
       <c r="C26" s="77" t="inlineStr">
         <is>
           <t>会社説明はインプットだけで完結させる。発言・考える・発表を一切求めない。5分を厳守し、最後は「後半戦への期待感」で締めることで雰囲気を維持する。</t>
         </is>
       </c>
-      <c r="D26" s="71" t="n"/>
-      <c r="E26" s="71" t="n"/>
-      <c r="F26" s="71" t="n"/>
-      <c r="G26" s="71" t="n"/>
-      <c r="H26" s="71" t="n"/>
+      <c r="D26" s="91" t="n"/>
+      <c r="E26" s="91" t="n"/>
+      <c r="F26" s="91" t="n"/>
+      <c r="G26" s="91" t="n"/>
+      <c r="H26" s="92" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -4873,16 +4896,1228 @@
     <mergeCell ref="C24:H24"/>
     <mergeCell ref="A26:B26"/>
     <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C26:H26"/>
+    <mergeCell ref="A5:H5"/>
     <mergeCell ref="C22:H22"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="C23:H23"/>
-    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="C26:H26"/>
     <mergeCell ref="A8:H8"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="A17:H17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="70" t="inlineStr">
+        <is>
+          <t>27新卒 内定承諾者向け 顔合わせ企画書（Zoom・60分）　【構成改訂版 v3】</t>
+        </is>
+      </c>
+      <c r="B1" s="71" t="n"/>
+      <c r="C1" s="71" t="n"/>
+      <c r="D1" s="71" t="n"/>
+      <c r="E1" s="71" t="n"/>
+      <c r="F1" s="71" t="n"/>
+      <c r="G1" s="71" t="n"/>
+      <c r="H1" s="71" t="n"/>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="72" t="inlineStr">
+        <is>
+          <t>参加者：内定承諾者 各グループ ＋ 人事担当　／　形式：Zoom　／　総時間：55〜60分</t>
+        </is>
+      </c>
+      <c r="B2" s="71" t="n"/>
+      <c r="C2" s="71" t="n"/>
+      <c r="D2" s="71" t="n"/>
+      <c r="E2" s="71" t="n"/>
+      <c r="F2" s="71" t="n"/>
+      <c r="G2" s="71" t="n"/>
+      <c r="H2" s="71" t="n"/>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="73" t="inlineStr">
+        <is>
+          <t>■ v3の設計思想</t>
+        </is>
+      </c>
+      <c r="B3" s="71" t="n"/>
+      <c r="C3" s="71" t="n"/>
+      <c r="D3" s="71" t="n"/>
+      <c r="E3" s="71" t="n"/>
+      <c r="F3" s="71" t="n"/>
+      <c r="G3" s="71" t="n"/>
+      <c r="H3" s="71" t="n"/>
+    </row>
+    <row r="4" ht="90" customHeight="1">
+      <c r="A4" s="75" t="inlineStr">
+        <is>
+          <t>【v2からの変更点】
+v2では前半・後半が別コンテンツのため「つながり」が薄かった。
+【v3の原則】
+前半と後半は「同一ワークの 前半＝グループ内で意見出し・準備 → 後半＝全体への発表・答え合わせ」として設計。
+会社説明はその間に挟む「自然な中断・休憩」として機能する。
+採用ワーク：「同期あるある予想ゲーム」
+前半でメンバーの行動・価値観を"予想"し、会社説明を挟んで後半で"答え合わせ"をする。
+「答えを知りたい」という宙ぶらりん感が、会社説明中の集中力を維持させる効果もある。</t>
+        </is>
+      </c>
+      <c r="B4" s="71" t="n"/>
+      <c r="C4" s="71" t="n"/>
+      <c r="D4" s="71" t="n"/>
+      <c r="E4" s="71" t="n"/>
+      <c r="F4" s="71" t="n"/>
+      <c r="G4" s="71" t="n"/>
+      <c r="H4" s="71" t="n"/>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="73" t="inlineStr">
+        <is>
+          <t>■ 全体タイムライン</t>
+        </is>
+      </c>
+      <c r="B5" s="71" t="n"/>
+      <c r="C5" s="71" t="n"/>
+      <c r="D5" s="71" t="n"/>
+      <c r="E5" s="71" t="n"/>
+      <c r="F5" s="71" t="n"/>
+      <c r="G5" s="71" t="n"/>
+      <c r="H5" s="71" t="n"/>
+    </row>
+    <row r="6" ht="50" customHeight="1">
+      <c r="A6" s="93" t="inlineStr">
+        <is>
+          <t>0〜5分
+流れ説明
++人事自己紹介</t>
+        </is>
+      </c>
+      <c r="B6" s="93" t="inlineStr">
+        <is>
+          <t>5〜15分
+アイスブレイク
+自己紹介リレー</t>
+        </is>
+      </c>
+      <c r="C6" s="94" t="inlineStr">
+        <is>
+          <t>15〜30分
+【同一ワーク前半】
+グループ内 予想タイム</t>
+        </is>
+      </c>
+      <c r="D6" s="95" t="inlineStr">
+        <is>
+          <t>30〜35分
+会社説明
+（休憩がてら）</t>
+        </is>
+      </c>
+      <c r="E6" s="94" t="inlineStr">
+        <is>
+          <t>35〜55分
+【同一ワーク後半】
+全体 答え合わせ発表</t>
+        </is>
+      </c>
+      <c r="F6" s="97" t="inlineStr">
+        <is>
+          <t>55〜60分
+クロージング
+次回予告</t>
+        </is>
+      </c>
+      <c r="H6" s="71" t="n"/>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="71" t="n"/>
+      <c r="B7" s="71" t="n"/>
+      <c r="C7" s="105" t="inlineStr">
+        <is>
+          <t>◀━━━━━ 同一ワーク「同期あるある予想ゲーム」 ━━━━━▶</t>
+        </is>
+      </c>
+      <c r="D7" s="71" t="n"/>
+      <c r="E7" s="71" t="n"/>
+      <c r="F7" s="71" t="n"/>
+      <c r="G7" s="71" t="n"/>
+      <c r="H7" s="71" t="n"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="73" t="inlineStr">
+        <is>
+          <t>■ メインワーク詳細：「同期あるある予想ゲーム」（前半15分 ＋ 後半20分 ＝ 計35分）</t>
+        </is>
+      </c>
+      <c r="B8" s="71" t="n"/>
+      <c r="C8" s="71" t="n"/>
+      <c r="D8" s="71" t="n"/>
+      <c r="E8" s="71" t="n"/>
+      <c r="F8" s="71" t="n"/>
+      <c r="G8" s="71" t="n"/>
+      <c r="H8" s="71" t="n"/>
+    </row>
+    <row r="9" ht="90" customHeight="1">
+      <c r="A9" s="106" t="inlineStr">
+        <is>
+          <t>【ゲームの流れ】
+①前半（グループ内）：人事が出した「このメンバーの中で〇〇な人は何人いる？」という質問に対して各自が予想し、グループ内で意見を出し合う
+②中断（会社説明5分）：「答えは後ほど！まず少しだけ会社の話を」で自然に挟む。答えを知りたい"宙ぶらりん感"が続くため参加者は話を聞きやすい状態になる
+③後半（全体）：実際に「〇〇な人は手を挙げて！」で答え合わせ。一番予想が当たった人を「同期マスター」として表彰する
+【このワークを選んだ理由】
+・前半と後半が「予想→答え合わせ」で完全にひとつながりになる
+・全員が必ず発言する構造になっている（手を挙げる・答える・エピソードを話す）
+・時間管理が容易（問題数を増減するだけで時間調整が可能）
+・会社説明を挟んでも「答えが知りたい」という気持ちで後半へ自然に戻れる</t>
+        </is>
+      </c>
+      <c r="B9" s="71" t="n"/>
+      <c r="C9" s="71" t="n"/>
+      <c r="D9" s="71" t="n"/>
+      <c r="E9" s="71" t="n"/>
+      <c r="F9" s="71" t="n"/>
+      <c r="G9" s="71" t="n"/>
+      <c r="H9" s="71" t="n"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="73" t="inlineStr">
+        <is>
+          <t>■ プログラム詳細</t>
+        </is>
+      </c>
+      <c r="B10" s="71" t="n"/>
+      <c r="C10" s="71" t="n"/>
+      <c r="D10" s="71" t="n"/>
+      <c r="E10" s="71" t="n"/>
+      <c r="F10" s="71" t="n"/>
+      <c r="G10" s="71" t="n"/>
+      <c r="H10" s="71" t="n"/>
+    </row>
+    <row r="11" ht="35" customHeight="1">
+      <c r="A11" s="76" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B11" s="76" t="inlineStr">
+        <is>
+          <t>コンテンツ名</t>
+        </is>
+      </c>
+      <c r="C11" s="76" t="inlineStr">
+        <is>
+          <t>時間
+（累計）</t>
+        </is>
+      </c>
+      <c r="D11" s="76" t="inlineStr">
+        <is>
+          <t>狙い（Why）</t>
+        </is>
+      </c>
+      <c r="E11" s="76" t="inlineStr">
+        <is>
+          <t>進行スクリプト（How）
+※かぎ括弧がそのまま使えるセリフ例</t>
+        </is>
+      </c>
+      <c r="F11" s="76" t="inlineStr">
+        <is>
+          <t>成功の判断基準</t>
+        </is>
+      </c>
+      <c r="G11" s="76" t="inlineStr">
+        <is>
+          <t>リスクと対策</t>
+        </is>
+      </c>
+      <c r="H11" s="76" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="130" customHeight="1">
+      <c r="A12" s="77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B12" s="98" t="inlineStr">
+        <is>
+          <t>入室待機
+・BGM</t>
+        </is>
+      </c>
+      <c r="C12" s="77" t="inlineStr">
+        <is>
+          <t>開始15分前
+（待機）</t>
+        </is>
+      </c>
+      <c r="D12" s="77" t="inlineStr">
+        <is>
+          <t>「この会社はちゃんとしている」という第一印象を開始前から形成する。緊張状態で入室する学生の不安を事前に下げる。</t>
+        </is>
+      </c>
+      <c r="E12" s="77" t="inlineStr">
+        <is>
+          <t>【準備チェックリスト】
+□ BGMを流す（Spotifyリラックス系推奨）
+□ 待機画面に「今日の流れ」スライドを表示
+□ チャットに「こんにちは！今日はよろしくお願いします😊 カメラONにしてもらえると嬉しいです！」を準備
+□ MC担当 / チャット＆タイム管理担当の役割確認
+□ 予想ゲームの問題リストを手元に用意（下記参照）
+【入室時の声かけ例】
+「〇〇さん、入ってくれましたね！今日はよろしくお願いします。全員揃うまで気楽にしていてください」</t>
+        </is>
+      </c>
+      <c r="F12" s="77" t="inlineStr">
+        <is>
+          <t>全員カメラON・笑顔で入室</t>
+        </is>
+      </c>
+      <c r="G12" s="77" t="inlineStr">
+        <is>
+          <t>無言入室が続く場合 → 個人名で「〇〇さん、今日どこから参加ですか？」と話しかける</t>
+        </is>
+      </c>
+      <c r="H12" s="77" t="inlineStr">
+        <is>
+          <t>開始5分前にリマインドをチャットで送る</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="130" customHeight="1">
+      <c r="A13" s="79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B13" s="99" t="inlineStr">
+        <is>
+          <t>流れ説明
+＋人事自己紹介</t>
+        </is>
+      </c>
+      <c r="C13" s="79" t="inlineStr">
+        <is>
+          <t>0〜5分
+（5分）</t>
+        </is>
+      </c>
+      <c r="D13" s="79" t="inlineStr">
+        <is>
+          <t>①ゴールを2つに絞って言語化することで参加者の心理的ハードルを下げる。②人事が先に自己開示することで「この場では自己開示してよい」という規範を示す（モデリング効果）。</t>
+        </is>
+      </c>
+      <c r="E13" s="79" t="inlineStr">
+        <is>
+          <t>【冒頭セリフ例（そのまま使用可）】
+「みなさん、こんにちは！今日は最初の顔合わせということでとても楽しみにしてきました。
+今日のゴールは2つだけ。①全員の顔と名前を覚える。②今日楽しかった、と思いながら画面を閉じる。それだけです！
+今日はゲームもありますので、ぜひ楽しんでいってください。まず私から自己紹介しますね。」
+【人事自己紹介の構成（60秒）】
+① 名前・担当業務（10秒）
+② 今ハマっていること・推し（具体的に、20秒）
+③ 意外な一面・ギャップ（20秒）
+④ 「今日はみなさんのことをもっと知りたくてきました！」（10秒）
+【ゲームの予告を冒頭で入れる（期待感を作る）】
+「今日は後半でゲームがあります。同期のことをどれだけ予想できるか、腕試しをしてもらいます（笑）お楽しみに！」</t>
+        </is>
+      </c>
+      <c r="F13" s="79" t="inlineStr">
+        <is>
+          <t>参加者が笑顔でうなずいている・「ゲームって何？」という期待感が生まれている</t>
+        </is>
+      </c>
+      <c r="G13" s="79" t="inlineStr">
+        <is>
+          <t>人事が緊張して棒読みになる → 必ず前日にリハーサルを実施する</t>
+        </is>
+      </c>
+      <c r="H13" s="79" t="inlineStr">
+        <is>
+          <t>スライド1枚：今日の流れ図を画面共有</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="130" customHeight="1">
+      <c r="A14" s="79" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B14" s="99" t="inlineStr">
+        <is>
+          <t>1分自己紹介
+リレー
+（アイスブレイク）</t>
+        </is>
+      </c>
+      <c r="C14" s="79" t="inlineStr">
+        <is>
+          <t>5〜15分
+（10分）</t>
+        </is>
+      </c>
+      <c r="D14" s="79" t="inlineStr">
+        <is>
+          <t>顔・名前・キャラクターを一致させる。後半の「予想ゲーム」の精度を上げるための情報収集フェーズでもある。指名形式で全員が必ず1度発言する。</t>
+        </is>
+      </c>
+      <c r="E14" s="79" t="inlineStr">
+        <is>
+          <t>【項目（画面共有で表示）】
+① 名前・大学
+② 最近の推し or マイブーム（何でもOK）→ 可能なら画面に映す
+③ 一言キャッチフレーズ
+（例："見た目は地味ですが熱量だけはあります"）
+【進行セリフ例】
+「自己紹介をしていきます。推しは何でもOK！最後に次の人を指名してバトンを渡してください。後で予想ゲームがあるので、みなさんの話をよく覚えておいてください（笑）。では〇〇さんからお願いします！」
+【チャット担当の動き（重要）】
+各発言に対してリアルタイムで反応を流す
+例：「〇〇大学！いいですね」「推し、わかります笑」
+→ スタンプ（拍手・ハート）を積極的に使う
+【参加者プロフィール活用（事前確認）】
+・富川（野球全国優勝）→「え、全国⁉」でチャットが沸く。早めに登場させる
+・折笠（甲子園チア部優勝・学祭委員長80名）→ 発表慣れあり。後半ゲームでもリード役
+・本多（キックボクシング）→「え、格闘技⁉」で盛り上がる
+・佐々木（評価1位・録音→ロープレ繰り返し）→「努力の天才」キャラとして紹介できる</t>
+        </is>
+      </c>
+      <c r="F14" s="79" t="inlineStr">
+        <is>
+          <t>全員が1回は笑いを取れている・チャットが賑わっている</t>
+        </is>
+      </c>
+      <c r="G14" s="79" t="inlineStr">
+        <is>
+          <t>一人が長くなる → 「いいですね！じゃあ次の方にバトンを」と自然に促す</t>
+        </is>
+      </c>
+      <c r="H14" s="79" t="inlineStr">
+        <is>
+          <t>事前に推しが分かるものを画面に映すよう案内</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="130" customHeight="1">
+      <c r="A15" s="81" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B15" s="89" t="inlineStr">
+        <is>
+          <t>【ワーク前半】
+同期あるある
+予想タイム
+（グループ内）</t>
+        </is>
+      </c>
+      <c r="C15" s="81" t="inlineStr">
+        <is>
+          <t>15〜30分
+（15分）</t>
+        </is>
+      </c>
+      <c r="D15" s="81" t="inlineStr">
+        <is>
+          <t>「このメンバーなら〇〇そう」という予想を立てることで相手への関心が高まる。グループ内で意見を出し合うことで会話が自然に深まる。「答えはまだわからない」宙ぶらりん感が、次の会社説明中も参加者を引きつける効果がある。</t>
+        </is>
+      </c>
+      <c r="E15" s="81" t="inlineStr">
+        <is>
+          <t>【ルール説明（画面共有で表示）】
+「今から問題を5〜7問出します。"このメンバーの中で〇〇な人は何人いる？"という問題です。各自が人数を予想して、グループ内で意見を出し合ってください。答え合わせは後半でやります！」
+【問題リスト（推奨7問）】
+問1：「犬を飼っている（飼ったことがある）人は何人？」
+問2：「海外旅行に行ったことがある人は何人？」
+問3：「電車やバスで寝過ごした経験がある人は何人？」
+問4：「0時前に寝るのが習慣の人は何人？」
+問5：「ひとりで映画館に行ったことがある人は何人？」
+問6：「最後の晩餐はラーメンを選ぶ人は何人？」
+問7：「今も実家暮らしの人は何人？」
+※問題は参加者プロフィールを見て事前にカスタマイズすると盛り上がる
+【進行セリフ例】
+「では予想タイムスタートです！問題を1問ずつ読み上げますので、各自紙やメモに人数を書いてください。グループ内で相談しながら予想してもOKです！」
+【全問読み上げ後のセリフ（前半→会社説明への橋渡し）】
+「予想は書けましたか？答えは後でのお楽しみです！ここで少しだけ脳を休めて、弊社のことを3分でお伝えしますね。"少しだけ"なので安心してください（笑）」</t>
+        </is>
+      </c>
+      <c r="F15" s="81" t="inlineStr">
+        <is>
+          <t>参加者が問題に対して声を出して反応している・グループ内で「えー何人だろう？」という会話が起きている</t>
+        </is>
+      </c>
+      <c r="G15" s="81" t="inlineStr">
+        <is>
+          <t>反応が薄い場合 → 「〇〇さんは何人だと思います？」と個人に振る
+問題が難しすぎる場合 → よりシンプルな問題に差し替える（例：「朝ごはんを毎日食べる人は？」）</t>
+        </is>
+      </c>
+      <c r="H15" s="81" t="inlineStr">
+        <is>
+          <t>問題は事前にスライドに入れておき一覧で見せてから予想させると進行しやすい</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="130" customHeight="1">
+      <c r="A16" s="85" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B16" s="100" t="inlineStr">
+        <is>
+          <t>会社説明
+（休憩がてら
+インプットのみ）</t>
+        </is>
+      </c>
+      <c r="C16" s="85" t="inlineStr">
+        <is>
+          <t>30〜35分
+（5分）</t>
+        </is>
+      </c>
+      <c r="D16" s="85" t="inlineStr">
+        <is>
+          <t>盛り上がったワーク前半の直後に「自然な休憩」として差し込む。「答えはまだわからない」という宙ぶらりん感が、参加者を会社説明中も集中させる効果がある。アウトプットは一切求めない。3つのキーワードを記憶に残すだけでよい。</t>
+        </is>
+      </c>
+      <c r="E16" s="85" t="inlineStr">
+        <is>
+          <t>【冒頭セリフ（警戒させないための言い回し）】
+「少しだけ弊社のことをお伝えさせてください。まだあまり知らない状態で入社するのも不安だと思うので、改めて簡単にご紹介します。3分だけお付き合いください！」
+【伝える3点（各1分・計3分）】
+①業界NO.1の安定性
+「人材派遣業界の中でも建設・インフラ特化で業界シェアトップクラスです。建設インフラは社会インフラそのものなので景気に左右されにくい特性があります。」
+②本社勤め・選ぶ側
+「皆さんは派遣される側ではなく、派遣する側・コーディネートする側です。毎日スーツで本社出社が基本で、現場仕事ではありません。」
+③大手グループの安定感
+「〇〇グループ傘下として、バックアップ体制もしっかりしています。」
+【締めセリフ（後半ゲームへのつなぎ）】
+「友達や親御さんに"どんな会社？"と聞かれたときこの3つを話すだけで説明になります。覚えておいてくださいね。
+では、お待ちかねの答え合わせをしましょうか！自分の予想は当たっているか！？後半戦スタートです！」</t>
+        </is>
+      </c>
+      <c r="F16" s="85" t="inlineStr">
+        <is>
+          <t>ネガティブな反応が出ていない・参加者がうなずいている</t>
+        </is>
+      </c>
+      <c r="G16" s="85" t="inlineStr">
+        <is>
+          <t>説明が長くなる → 必ず5分で切る
+暗い雰囲気になる → 後半の「答え合わせ」への期待感で締めることで雰囲気を維持する</t>
+        </is>
+      </c>
+      <c r="H16" s="85" t="inlineStr">
+        <is>
+          <t>説明会資料から該当スライドを最大3枚に絞る</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="130" customHeight="1">
+      <c r="A17" s="81" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B17" s="89" t="inlineStr">
+        <is>
+          <t>【ワーク後半】
+同期あるある
+答え合わせ発表
+（全体）</t>
+        </is>
+      </c>
+      <c r="C17" s="81" t="inlineStr">
+        <is>
+          <t>35〜55分
+（20分）</t>
+        </is>
+      </c>
+      <c r="D17" s="81" t="inlineStr">
+        <is>
+          <t>前半の「予想」に対して実際の「答え」が明らかになる瞬間が複数回生まれ、自然と盛り上がる。全員が必ず「手を挙げる・答える・エピソードを話す」の発言機会を持つ。一番予想が当たった人を表彰することで競争要素が加わり最後まで盛り上がりが持続する。</t>
+        </is>
+      </c>
+      <c r="E17" s="81" t="inlineStr">
+        <is>
+          <t>【進行セリフ例（そのまま使用可）】
+「お待たせしました！では答え合わせをしていきます！予想した人数が当たっていたら、チャットに"当たり！"と書いてください（笑）では問1からいきます！」
+【各問の進め方（1問あたり約2〜2.5分）】
+STEP1：人事が問題を読み上げる（10秒）
+STEP2：「〇〇な人は手を挙げて（またはカメラに近づいて）ください！」（5秒）
+STEP3：全員で数を数える（5秒）
+STEP4：予想が当たっていた人がチャットに書く（10秒）
+STEP5：手を挙げた人の中から1〜2人にエピソードを聞く（60〜90秒）
+→ 例：「〇〇さん、犬を飼っているんですね！何犬ですか？」「いつから飼ってるんですか？」
+【7問 × 約2.5分 ＝ 約17分】
+【残り3分：同期マスター発表】
+「では一番予想が当たった人を発表します！採点してみてください！」
+→ 各自が正解数をチャットに書く
+→ 一番多い人を「同期マスター」として表彰
+→ 「〇〇さん、なんでそんなに当たるんですか？（笑）」と一言コメントをもらう
+【締めセリフ（クロージングへの橋渡し）】
+「いや〜、思った以上に盛り上がりましたね！今日だけで〇〇さんが実は犬4匹飼ってるとか（笑）、なんか一気に仲間感が出た気がします！」</t>
+        </is>
+      </c>
+      <c r="F17" s="81" t="inlineStr">
+        <is>
+          <t>全7問で参加者の発言が1回以上ある・笑いが3回以上起きている・「同期マスター」表彰で締めくくれている</t>
+        </is>
+      </c>
+      <c r="G17" s="81" t="inlineStr">
+        <is>
+          <t>問ごとに誰も手を挙げない問題が出る → 「意外！じゃあ次は絶対いると思った人は？」と続けて盛り上げる
+時間が余る → エピソードを深掘りする問題を増やす
+時間が足りない → 残り問題を1問ずつ手を挙げるだけ（エピソードなし）で答え合わせ</t>
+        </is>
+      </c>
+      <c r="H17" s="81" t="inlineStr">
+        <is>
+          <t>6/23（女子4名）は深掘り重視で1問あたり3分取れる。6/30（混合6名）は1問2分ペースで進める</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="130" customHeight="1">
+      <c r="A18" s="103" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B18" s="104" t="inlineStr">
+        <is>
+          <t>クロージング
+＋次回予告</t>
+        </is>
+      </c>
+      <c r="C18" s="103" t="inlineStr">
+        <is>
+          <t>55〜60分
+（5分）</t>
+        </is>
+      </c>
+      <c r="D18" s="103" t="inlineStr">
+        <is>
+          <t>「またこのメンバーに会いたい」という感情で終わらせる。次のイベントへの期待値を上げ入社までの緩やかなつながりを維持する。アンケートで本音を収集し次回以降に活かす。</t>
+        </is>
+      </c>
+      <c r="E18" s="103" t="inlineStr">
+        <is>
+          <t>【締めセリフ例（そのまま使用可）】
+「今日はありがとうございました！正直、最初はどんな会話になるか少し緊張していたんですが、みなさんのおかげでとても盛り上がりましたね。
+今日だけで〇〇さんが実は犬4匹飼ってるとか（笑）、△△さんが毎朝5時起きとか、一気に仲間感が出た気がしています。
+次は〇月〇日に対面での顔合わせを予定しています。今度は直接会えるのが楽しみです！それまでも何かあれば遠慮なく私に連絡してください。連絡先はチャットに貼りますね。
+では最後にアンケートだけお願いします。1分で終わります！URLをチャットに貼ります。」
+【チャットに貼るもの（事前にコピー準備）】
+□ アンケートフォームURL
+□ 次回日程（テキスト）
+□ 人事担当の連絡先（LINE or メール）
+【アンケート項目（5問・1分以内）】
+① 今日の満足度（5段階）
+② 一番楽しかったコンテンツ（選択式）
+③ 入社に対して不安に思っていることがあれば（自由記述・任意）
+④ 次回も参加したいと思えましたか（Yes/No）
+⑤ 一言感想（任意）</t>
+        </is>
+      </c>
+      <c r="F18" s="103" t="inlineStr">
+        <is>
+          <t>参加者全員がアンケートを送信・次回日程をスケジュール登録</t>
+        </is>
+      </c>
+      <c r="G18" s="103" t="inlineStr">
+        <is>
+          <t>時間オーバーの場合 → 同期マスターの表彰を省略しクロージングを優先
+クロージングの5分は絶対に削らない</t>
+        </is>
+      </c>
+      <c r="H18" s="103" t="inlineStr">
+        <is>
+          <t>クロージング後に5〜10分の任意雑談タイムを設けると帰属意識が上がる</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="73" t="inlineStr">
+        <is>
+          <t>■ 予想ゲーム 問題リスト詳細（人事用・事前準備）</t>
+        </is>
+      </c>
+      <c r="B19" s="71" t="n"/>
+      <c r="C19" s="71" t="n"/>
+      <c r="D19" s="71" t="n"/>
+      <c r="E19" s="71" t="n"/>
+      <c r="F19" s="71" t="n"/>
+      <c r="G19" s="71" t="n"/>
+      <c r="H19" s="71" t="n"/>
+    </row>
+    <row r="20" ht="25" customHeight="1">
+      <c r="A20" s="76" t="inlineStr">
+        <is>
+          <t>問番号</t>
+        </is>
+      </c>
+      <c r="B20" s="76" t="inlineStr">
+        <is>
+          <t>問題文</t>
+        </is>
+      </c>
+      <c r="C20" s="76" t="inlineStr">
+        <is>
+          <t>狙い・期待される反応</t>
+        </is>
+      </c>
+      <c r="D20" s="76" t="inlineStr">
+        <is>
+          <t>エピソードを聞く候補（事前確認）</t>
+        </is>
+      </c>
+      <c r="E20" s="76" t="inlineStr">
+        <is>
+          <t>難易度</t>
+        </is>
+      </c>
+      <c r="F20" s="76" t="inlineStr">
+        <is>
+          <t>時間目安</t>
+        </is>
+      </c>
+      <c r="G20" s="76" t="inlineStr"/>
+      <c r="H20" s="76" t="inlineStr"/>
+    </row>
+    <row r="21" ht="55" customHeight="1">
+      <c r="A21" s="81" t="inlineStr">
+        <is>
+          <t>問1</t>
+        </is>
+      </c>
+      <c r="B21" s="81" t="inlineStr">
+        <is>
+          <t>犬を飼っている（飼ったことがある）人は何人？</t>
+        </is>
+      </c>
+      <c r="C21" s="81" t="inlineStr">
+        <is>
+          <t>動物の話は共感を生みやすく、盛り上がりが安定している</t>
+        </is>
+      </c>
+      <c r="D21" s="81" t="inlineStr">
+        <is>
+          <t>西山（ランニング・キャディ）→ 意外に動物を飼っているかも。本多（犬好きな格闘家）→ ギャップで盛り上がる可能性</t>
+        </is>
+      </c>
+      <c r="E21" s="81" t="inlineStr">
+        <is>
+          <t>★☆☆</t>
+        </is>
+      </c>
+      <c r="F21" s="81" t="inlineStr">
+        <is>
+          <t>2〜3分</t>
+        </is>
+      </c>
+      <c r="G21" s="81" t="inlineStr"/>
+      <c r="H21" s="81" t="inlineStr"/>
+    </row>
+    <row r="22" ht="55" customHeight="1">
+      <c r="A22" s="77" t="inlineStr">
+        <is>
+          <t>問2</t>
+        </is>
+      </c>
+      <c r="B22" s="77" t="inlineStr">
+        <is>
+          <t>海外旅行に行ったことがある人は何人？</t>
+        </is>
+      </c>
+      <c r="C22" s="77" t="inlineStr">
+        <is>
+          <t>経験の差が出る問題。「どこ？」の深掘りで話が広がりやすい</t>
+        </is>
+      </c>
+      <c r="D22" s="77" t="inlineStr">
+        <is>
+          <t>折笠（仙台育英・チア部）→ 遠征や海外チアの経験があるかも
+市川（スタバ・好奇心旺盛）→ 海外経験ありそう</t>
+        </is>
+      </c>
+      <c r="E22" s="77" t="inlineStr">
+        <is>
+          <t>★☆☆</t>
+        </is>
+      </c>
+      <c r="F22" s="77" t="inlineStr">
+        <is>
+          <t>2〜3分</t>
+        </is>
+      </c>
+      <c r="G22" s="77" t="inlineStr"/>
+      <c r="H22" s="77" t="inlineStr"/>
+    </row>
+    <row r="23" ht="55" customHeight="1">
+      <c r="A23" s="81" t="inlineStr">
+        <is>
+          <t>問3</t>
+        </is>
+      </c>
+      <c r="B23" s="81" t="inlineStr">
+        <is>
+          <t>電車やバスで寝過ごした経験がある人は何人？</t>
+        </is>
+      </c>
+      <c r="C23" s="81" t="inlineStr">
+        <is>
+          <t>「失敗談」は笑いに変わりやすく心理的安全性を高める</t>
+        </is>
+      </c>
+      <c r="D23" s="81" t="inlineStr">
+        <is>
+          <t>全員が体験している可能性があり、全員が発言しやすい</t>
+        </is>
+      </c>
+      <c r="E23" s="81" t="inlineStr">
+        <is>
+          <t>★☆☆</t>
+        </is>
+      </c>
+      <c r="F23" s="81" t="inlineStr">
+        <is>
+          <t>2分</t>
+        </is>
+      </c>
+      <c r="G23" s="81" t="inlineStr"/>
+      <c r="H23" s="81" t="inlineStr"/>
+    </row>
+    <row r="24" ht="55" customHeight="1">
+      <c r="A24" s="77" t="inlineStr">
+        <is>
+          <t>問4</t>
+        </is>
+      </c>
+      <c r="B24" s="77" t="inlineStr">
+        <is>
+          <t>0時前に寝るのが習慣の人は何人？</t>
+        </is>
+      </c>
+      <c r="C24" s="77" t="inlineStr">
+        <is>
+          <t>生活リズムの違いが出て「え、早っ！」という反応が生まれやすい</t>
+        </is>
+      </c>
+      <c r="D24" s="77" t="inlineStr">
+        <is>
+          <t>佐々木（録音→ロープレ繰り返し）→ 勉強熱心なら遅寝かも
+西山（ランニング・陸上）→ 早寝早起きの可能性大</t>
+        </is>
+      </c>
+      <c r="E24" s="77" t="inlineStr">
+        <is>
+          <t>★★☆</t>
+        </is>
+      </c>
+      <c r="F24" s="77" t="inlineStr">
+        <is>
+          <t>2分</t>
+        </is>
+      </c>
+      <c r="G24" s="77" t="inlineStr"/>
+      <c r="H24" s="77" t="inlineStr"/>
+    </row>
+    <row r="25" ht="55" customHeight="1">
+      <c r="A25" s="81" t="inlineStr">
+        <is>
+          <t>問5</t>
+        </is>
+      </c>
+      <c r="B25" s="81" t="inlineStr">
+        <is>
+          <t>ひとりで映画館に行ったことがある人は何人？</t>
+        </is>
+      </c>
+      <c r="C25" s="81" t="inlineStr">
+        <is>
+          <t>「ひとり行動」派かどうかが出る。意外な回答が出やすい</t>
+        </is>
+      </c>
+      <c r="D25" s="81" t="inlineStr">
+        <is>
+          <t>荒井（心理学・ホスピタリティ）→ インドア系で一人映画ありそう
+根本（肝が据わっている）→ 堂々と一人行動していそう</t>
+        </is>
+      </c>
+      <c r="E25" s="81" t="inlineStr">
+        <is>
+          <t>★★☆</t>
+        </is>
+      </c>
+      <c r="F25" s="81" t="inlineStr">
+        <is>
+          <t>2分</t>
+        </is>
+      </c>
+      <c r="G25" s="81" t="inlineStr"/>
+      <c r="H25" s="81" t="inlineStr"/>
+    </row>
+    <row r="26" ht="55" customHeight="1">
+      <c r="A26" s="77" t="inlineStr">
+        <is>
+          <t>問6</t>
+        </is>
+      </c>
+      <c r="B26" s="77" t="inlineStr">
+        <is>
+          <t>最後の晩餐はラーメンを選ぶ人は何人？</t>
+        </is>
+      </c>
+      <c r="C26" s="77" t="inlineStr">
+        <is>
+          <t>食の好みは会話のきっかけになりやすく、「じゃあ何食べる？」と話が広がる</t>
+        </is>
+      </c>
+      <c r="D26" s="77" t="inlineStr">
+        <is>
+          <t>富川（野球少年・全寮制）→ 寮食育ちなので意外な答えかも
+本多（九州出身）→ 「博多ラーメン！」などで盛り上がる可能性</t>
+        </is>
+      </c>
+      <c r="E26" s="77" t="inlineStr">
+        <is>
+          <t>★☆☆</t>
+        </is>
+      </c>
+      <c r="F26" s="77" t="inlineStr">
+        <is>
+          <t>2〜3分</t>
+        </is>
+      </c>
+      <c r="G26" s="77" t="inlineStr"/>
+      <c r="H26" s="77" t="inlineStr"/>
+    </row>
+    <row r="27" ht="55" customHeight="1">
+      <c r="A27" s="81" t="inlineStr">
+        <is>
+          <t>問7</t>
+        </is>
+      </c>
+      <c r="B27" s="81" t="inlineStr">
+        <is>
+          <t>入社まで実家暮らしの人は何人？</t>
+        </is>
+      </c>
+      <c r="C27" s="81" t="inlineStr">
+        <is>
+          <t>「一人暮らし」vs「実家」でリアルな入社前の状況が見えて親近感が生まれる</t>
+        </is>
+      </c>
+      <c r="D27" s="81" t="inlineStr">
+        <is>
+          <t>折笠（仙台出身）・佐々木（福岡）・本多（九州）→ 上京・転居の話に広がりやすい</t>
+        </is>
+      </c>
+      <c r="E27" s="81" t="inlineStr">
+        <is>
+          <t>★☆☆</t>
+        </is>
+      </c>
+      <c r="F27" s="81" t="inlineStr">
+        <is>
+          <t>2分</t>
+        </is>
+      </c>
+      <c r="G27" s="81" t="inlineStr"/>
+      <c r="H27" s="81" t="inlineStr"/>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="73" t="inlineStr">
+        <is>
+          <t>■ グループ割り振り詳細</t>
+        </is>
+      </c>
+      <c r="B28" s="71" t="n"/>
+      <c r="C28" s="71" t="n"/>
+      <c r="D28" s="71" t="n"/>
+      <c r="E28" s="71" t="n"/>
+      <c r="F28" s="71" t="n"/>
+      <c r="G28" s="71" t="n"/>
+      <c r="H28" s="71" t="n"/>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="76" t="inlineStr">
+        <is>
+          <t>日程</t>
+        </is>
+      </c>
+      <c r="B29" s="76" t="inlineStr">
+        <is>
+          <t>規模・構成</t>
+        </is>
+      </c>
+      <c r="C29" s="76" t="inlineStr">
+        <is>
+          <t>参加者</t>
+        </is>
+      </c>
+      <c r="D29" s="76" t="inlineStr">
+        <is>
+          <t>予想ゲーム 進行のポイント</t>
+        </is>
+      </c>
+      <c r="E29" s="76" t="inlineStr">
+        <is>
+          <t>担当人事</t>
+        </is>
+      </c>
+      <c r="F29" s="76" t="inlineStr">
+        <is>
+          <t>特記事項</t>
+        </is>
+      </c>
+      <c r="G29" s="76" t="inlineStr"/>
+      <c r="H29" s="76" t="inlineStr"/>
+    </row>
+    <row r="30" ht="85" customHeight="1">
+      <c r="A30" s="89" t="inlineStr">
+        <is>
+          <t>2026/6/23
+11:00〜12:00</t>
+        </is>
+      </c>
+      <c r="B30" s="81" t="inlineStr">
+        <is>
+          <t>4名
+女性のみ</t>
+        </is>
+      </c>
+      <c r="C30" s="81" t="inlineStr">
+        <is>
+          <t>市川 結菜（神奈川大学）
+柳澤 明（東京経済大学）
+荒井 翠（駒澤大学）
+根本 彩花（東京富士大学）</t>
+        </is>
+      </c>
+      <c r="D30" s="81" t="inlineStr">
+        <is>
+          <t>少人数のため1問あたり3分取れる。エピソードを深掘りする方向で進める。
+予想タイムはグループ全員で話し合いながら進める形式でOK（ブレイクアウト不要）。
+「同期マスター」表彰はぜひ実施。4名全員が接戦になりやすく盛り上がる。</t>
+        </is>
+      </c>
+      <c r="E30" s="81" t="inlineStr">
+        <is>
+          <t>齋藤（MC）
+もう1名（チャット管理）</t>
+        </is>
+      </c>
+      <c r="F30" s="81" t="inlineStr">
+        <is>
+          <t>全員女性のため共感ベースの会話になりやすい。エピソードの深掘りを積極的に行う。</t>
+        </is>
+      </c>
+      <c r="G30" s="81" t="inlineStr"/>
+      <c r="H30" s="81" t="inlineStr"/>
+    </row>
+    <row r="31" ht="85" customHeight="1">
+      <c r="A31" s="90" t="inlineStr">
+        <is>
+          <t>2026/6/30
+15:00〜16:00</t>
+        </is>
+      </c>
+      <c r="B31" s="83" t="inlineStr">
+        <is>
+          <t>6名
+女3・男3</t>
+        </is>
+      </c>
+      <c r="C31" s="83" t="inlineStr">
+        <is>
+          <t>富川 哲太（大阪経済大学）
+西山 心町（東海大学）
+吉田 雅野（大東文化大学）
+折笠 未來美（仙台白百合女子大学）
+佐々木 七都（福岡大学）
+本多 諒（九州産業大学）</t>
+        </is>
+      </c>
+      <c r="D31" s="83" t="inlineStr">
+        <is>
+          <t>1問あたり2分ペースで進める。エピソードは1人に絞って深掘り。
+本多（ボクサー）の回答が場を沸かせる可能性大 → 早めの問題で登場させると後半の盛り上がりが続く。
+男女混合のため予想の差が出やすく「え、そうなの！？」が生まれやすい。</t>
+        </is>
+      </c>
+      <c r="E31" s="83" t="inlineStr">
+        <is>
+          <t>齋藤（MC）
+もう1名（チャット管理）</t>
+        </is>
+      </c>
+      <c r="F31" s="83" t="inlineStr">
+        <is>
+          <t>男女混合で自然と盛り上がりやすい。時間管理をしっかり行う。</t>
+        </is>
+      </c>
+      <c r="G31" s="83" t="inlineStr"/>
+      <c r="H31" s="83" t="inlineStr"/>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="73" t="inlineStr">
+        <is>
+          <t>■ 成功させるための5つのポイント</t>
+        </is>
+      </c>
+      <c r="B32" s="71" t="n"/>
+      <c r="C32" s="71" t="n"/>
+      <c r="D32" s="71" t="n"/>
+      <c r="E32" s="71" t="n"/>
+      <c r="F32" s="71" t="n"/>
+      <c r="G32" s="71" t="n"/>
+      <c r="H32" s="71" t="n"/>
+    </row>
+    <row r="33" ht="40" customHeight="1">
+      <c r="A33" s="80" t="inlineStr">
+        <is>
+          <t>✔ カメラON徹底</t>
+        </is>
+      </c>
+      <c r="B33" s="71" t="n"/>
+      <c r="C33" s="77" t="inlineStr">
+        <is>
+          <t>事前メールに「交流が目的なのでカメラONでご参加ください」と明記。当日冒頭でも笑顔でお願いする。</t>
+        </is>
+      </c>
+      <c r="D33" s="71" t="n"/>
+      <c r="E33" s="71" t="n"/>
+      <c r="F33" s="71" t="n"/>
+      <c r="G33" s="71" t="n"/>
+      <c r="H33" s="71" t="n"/>
+    </row>
+    <row r="34" ht="40" customHeight="1">
+      <c r="A34" s="80" t="inlineStr">
+        <is>
+          <t>✔ 人事が一番楽しむ</t>
+        </is>
+      </c>
+      <c r="B34" s="71" t="n"/>
+      <c r="C34" s="77" t="inlineStr">
+        <is>
+          <t>人事担当者がテンション1.2倍。予想ゲームでも「私も予想します！」と参加すると場が温まる。</t>
+        </is>
+      </c>
+      <c r="D34" s="71" t="n"/>
+      <c r="E34" s="71" t="n"/>
+      <c r="F34" s="71" t="n"/>
+      <c r="G34" s="71" t="n"/>
+      <c r="H34" s="71" t="n"/>
+    </row>
+    <row r="35" ht="40" customHeight="1">
+      <c r="A35" s="80" t="inlineStr">
+        <is>
+          <t>✔ 問題を事前にカスタマイズ</t>
+        </is>
+      </c>
+      <c r="B35" s="71" t="n"/>
+      <c r="C35" s="77" t="inlineStr">
+        <is>
+          <t>内定承諾者のプロフィール（スポーツ経験・出身地・バイト）を見て問題をカスタマイズすると「これ私のこと知ってる？」という驚きと笑いが生まれる。</t>
+        </is>
+      </c>
+      <c r="D35" s="71" t="n"/>
+      <c r="E35" s="71" t="n"/>
+      <c r="F35" s="71" t="n"/>
+      <c r="G35" s="71" t="n"/>
+      <c r="H35" s="71" t="n"/>
+    </row>
+    <row r="36" ht="40" customHeight="1">
+      <c r="A36" s="80" t="inlineStr">
+        <is>
+          <t>✔ 会社説明の5分を厳守</t>
+        </is>
+      </c>
+      <c r="B36" s="71" t="n"/>
+      <c r="C36" s="77" t="inlineStr">
+        <is>
+          <t>「答えはまだわからない」宙ぶらりん感が後半への期待を作る。会社説明が長引くとその効果が消える。5分を必ず守る。</t>
+        </is>
+      </c>
+      <c r="D36" s="71" t="n"/>
+      <c r="E36" s="71" t="n"/>
+      <c r="F36" s="71" t="n"/>
+      <c r="G36" s="71" t="n"/>
+      <c r="H36" s="71" t="n"/>
+    </row>
+    <row r="37" ht="40" customHeight="1">
+      <c r="A37" s="80" t="inlineStr">
+        <is>
+          <t>✔ エピソードの深掘りが鍵</t>
+        </is>
+      </c>
+      <c r="B37" s="71" t="n"/>
+      <c r="C37" s="77" t="inlineStr">
+        <is>
+          <t>答え合わせで手を挙げた人に「どんな経緯で？」と一言聞くだけで場が温まる。深掘りの質を人事が担うことで会話の密度が上がる。</t>
+        </is>
+      </c>
+      <c r="D37" s="71" t="n"/>
+      <c r="E37" s="71" t="n"/>
+      <c r="F37" s="71" t="n"/>
+      <c r="G37" s="71" t="n"/>
+      <c r="H37" s="71" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="22">
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="C36:H36"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="C37:H37"/>
+    <mergeCell ref="C34:H34"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A32:H32"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="C33:H33"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A28:H28"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="C35:H35"/>
+    <mergeCell ref="A34:B34"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/6月顔合わせ企画書_改善版.xlsx
+++ b/6月顔合わせ企画書_改善版.xlsx
@@ -14,6 +14,7 @@
     <sheet name="【改善版】6月顔合わせ企画書" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="【改善版v2】6月企画書" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="【改善版v3】6月企画書" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="【改善版v4】6月企画書" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191028" fullCalcOnLoad="1"/>
@@ -23,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="34">
+  <fonts count="36">
     <font>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
@@ -249,8 +250,16 @@
       <color rgb="00375623"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="14">
+  <fills count="18">
     <fill>
       <patternFill/>
     </fill>
@@ -329,8 +338,29 @@
         <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
+        <bgColor rgb="00D9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+        <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="32">
+  <borders count="34">
     <border>
       <left/>
       <right/>
@@ -698,11 +728,39 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="00000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="00000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="107">
+  <cellXfs count="122">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -934,6 +992,45 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="8" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="16" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="17" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="16" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="17" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="15" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="17" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="17" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="17" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4019,7 +4116,7 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="C20:H20"/>
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A21:B21"/>
@@ -4031,7 +4128,7 @@
     <mergeCell ref="C22:H22"/>
     <mergeCell ref="A13:H13"/>
     <mergeCell ref="C18:H18"/>
-    <mergeCell ref="C20:H20"/>
+    <mergeCell ref="A1:H1"/>
     <mergeCell ref="A18:B18"/>
     <mergeCell ref="C21:H21"/>
     <mergeCell ref="A22:B22"/>
@@ -4896,12 +4993,12 @@
     <mergeCell ref="C24:H24"/>
     <mergeCell ref="A26:B26"/>
     <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="C26:H26"/>
     <mergeCell ref="C22:H22"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="C23:H23"/>
-    <mergeCell ref="C26:H26"/>
+    <mergeCell ref="A5:H5"/>
     <mergeCell ref="A8:H8"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="A17:H17"/>
@@ -4935,13 +5032,13 @@
           <t>27新卒 内定承諾者向け 顔合わせ企画書（Zoom・60分）　【構成改訂版 v3】</t>
         </is>
       </c>
-      <c r="B1" s="71" t="n"/>
-      <c r="C1" s="71" t="n"/>
-      <c r="D1" s="71" t="n"/>
-      <c r="E1" s="71" t="n"/>
-      <c r="F1" s="71" t="n"/>
-      <c r="G1" s="71" t="n"/>
-      <c r="H1" s="71" t="n"/>
+      <c r="B1" s="91" t="n"/>
+      <c r="C1" s="91" t="n"/>
+      <c r="D1" s="91" t="n"/>
+      <c r="E1" s="91" t="n"/>
+      <c r="F1" s="91" t="n"/>
+      <c r="G1" s="91" t="n"/>
+      <c r="H1" s="92" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="72" t="inlineStr">
@@ -4949,13 +5046,13 @@
           <t>参加者：内定承諾者 各グループ ＋ 人事担当　／　形式：Zoom　／　総時間：55〜60分</t>
         </is>
       </c>
-      <c r="B2" s="71" t="n"/>
-      <c r="C2" s="71" t="n"/>
-      <c r="D2" s="71" t="n"/>
-      <c r="E2" s="71" t="n"/>
-      <c r="F2" s="71" t="n"/>
-      <c r="G2" s="71" t="n"/>
-      <c r="H2" s="71" t="n"/>
+      <c r="B2" s="91" t="n"/>
+      <c r="C2" s="91" t="n"/>
+      <c r="D2" s="91" t="n"/>
+      <c r="E2" s="91" t="n"/>
+      <c r="F2" s="91" t="n"/>
+      <c r="G2" s="91" t="n"/>
+      <c r="H2" s="92" t="n"/>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="73" t="inlineStr">
@@ -4963,13 +5060,13 @@
           <t>■ v3の設計思想</t>
         </is>
       </c>
-      <c r="B3" s="71" t="n"/>
-      <c r="C3" s="71" t="n"/>
-      <c r="D3" s="71" t="n"/>
-      <c r="E3" s="71" t="n"/>
-      <c r="F3" s="71" t="n"/>
-      <c r="G3" s="71" t="n"/>
-      <c r="H3" s="71" t="n"/>
+      <c r="B3" s="91" t="n"/>
+      <c r="C3" s="91" t="n"/>
+      <c r="D3" s="91" t="n"/>
+      <c r="E3" s="91" t="n"/>
+      <c r="F3" s="91" t="n"/>
+      <c r="G3" s="91" t="n"/>
+      <c r="H3" s="92" t="n"/>
     </row>
     <row r="4" ht="90" customHeight="1">
       <c r="A4" s="75" t="inlineStr">
@@ -4984,13 +5081,13 @@
 「答えを知りたい」という宙ぶらりん感が、会社説明中の集中力を維持させる効果もある。</t>
         </is>
       </c>
-      <c r="B4" s="71" t="n"/>
-      <c r="C4" s="71" t="n"/>
-      <c r="D4" s="71" t="n"/>
-      <c r="E4" s="71" t="n"/>
-      <c r="F4" s="71" t="n"/>
-      <c r="G4" s="71" t="n"/>
-      <c r="H4" s="71" t="n"/>
+      <c r="B4" s="91" t="n"/>
+      <c r="C4" s="91" t="n"/>
+      <c r="D4" s="91" t="n"/>
+      <c r="E4" s="91" t="n"/>
+      <c r="F4" s="91" t="n"/>
+      <c r="G4" s="91" t="n"/>
+      <c r="H4" s="92" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="73" t="inlineStr">
@@ -4998,13 +5095,13 @@
           <t>■ 全体タイムライン</t>
         </is>
       </c>
-      <c r="B5" s="71" t="n"/>
-      <c r="C5" s="71" t="n"/>
-      <c r="D5" s="71" t="n"/>
-      <c r="E5" s="71" t="n"/>
-      <c r="F5" s="71" t="n"/>
-      <c r="G5" s="71" t="n"/>
-      <c r="H5" s="71" t="n"/>
+      <c r="B5" s="91" t="n"/>
+      <c r="C5" s="91" t="n"/>
+      <c r="D5" s="91" t="n"/>
+      <c r="E5" s="91" t="n"/>
+      <c r="F5" s="91" t="n"/>
+      <c r="G5" s="91" t="n"/>
+      <c r="H5" s="92" t="n"/>
     </row>
     <row r="6" ht="50" customHeight="1">
       <c r="A6" s="93" t="inlineStr">
@@ -5059,8 +5156,8 @@
           <t>◀━━━━━ 同一ワーク「同期あるある予想ゲーム」 ━━━━━▶</t>
         </is>
       </c>
-      <c r="D7" s="71" t="n"/>
-      <c r="E7" s="71" t="n"/>
+      <c r="D7" s="91" t="n"/>
+      <c r="E7" s="92" t="n"/>
       <c r="F7" s="71" t="n"/>
       <c r="G7" s="71" t="n"/>
       <c r="H7" s="71" t="n"/>
@@ -5071,13 +5168,13 @@
           <t>■ メインワーク詳細：「同期あるある予想ゲーム」（前半15分 ＋ 後半20分 ＝ 計35分）</t>
         </is>
       </c>
-      <c r="B8" s="71" t="n"/>
-      <c r="C8" s="71" t="n"/>
-      <c r="D8" s="71" t="n"/>
-      <c r="E8" s="71" t="n"/>
-      <c r="F8" s="71" t="n"/>
-      <c r="G8" s="71" t="n"/>
-      <c r="H8" s="71" t="n"/>
+      <c r="B8" s="91" t="n"/>
+      <c r="C8" s="91" t="n"/>
+      <c r="D8" s="91" t="n"/>
+      <c r="E8" s="91" t="n"/>
+      <c r="F8" s="91" t="n"/>
+      <c r="G8" s="91" t="n"/>
+      <c r="H8" s="92" t="n"/>
     </row>
     <row r="9" ht="90" customHeight="1">
       <c r="A9" s="106" t="inlineStr">
@@ -5093,13 +5190,13 @@
 ・会社説明を挟んでも「答えが知りたい」という気持ちで後半へ自然に戻れる</t>
         </is>
       </c>
-      <c r="B9" s="71" t="n"/>
-      <c r="C9" s="71" t="n"/>
-      <c r="D9" s="71" t="n"/>
-      <c r="E9" s="71" t="n"/>
-      <c r="F9" s="71" t="n"/>
-      <c r="G9" s="71" t="n"/>
-      <c r="H9" s="71" t="n"/>
+      <c r="B9" s="91" t="n"/>
+      <c r="C9" s="91" t="n"/>
+      <c r="D9" s="91" t="n"/>
+      <c r="E9" s="91" t="n"/>
+      <c r="F9" s="91" t="n"/>
+      <c r="G9" s="91" t="n"/>
+      <c r="H9" s="92" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="73" t="inlineStr">
@@ -5107,13 +5204,13 @@
           <t>■ プログラム詳細</t>
         </is>
       </c>
-      <c r="B10" s="71" t="n"/>
-      <c r="C10" s="71" t="n"/>
-      <c r="D10" s="71" t="n"/>
-      <c r="E10" s="71" t="n"/>
-      <c r="F10" s="71" t="n"/>
-      <c r="G10" s="71" t="n"/>
-      <c r="H10" s="71" t="n"/>
+      <c r="B10" s="91" t="n"/>
+      <c r="C10" s="91" t="n"/>
+      <c r="D10" s="91" t="n"/>
+      <c r="E10" s="91" t="n"/>
+      <c r="F10" s="91" t="n"/>
+      <c r="G10" s="91" t="n"/>
+      <c r="H10" s="92" t="n"/>
     </row>
     <row r="11" ht="35" customHeight="1">
       <c r="A11" s="76" t="inlineStr">
@@ -5571,13 +5668,13 @@
           <t>■ 予想ゲーム 問題リスト詳細（人事用・事前準備）</t>
         </is>
       </c>
-      <c r="B19" s="71" t="n"/>
-      <c r="C19" s="71" t="n"/>
-      <c r="D19" s="71" t="n"/>
-      <c r="E19" s="71" t="n"/>
-      <c r="F19" s="71" t="n"/>
-      <c r="G19" s="71" t="n"/>
-      <c r="H19" s="71" t="n"/>
+      <c r="B19" s="91" t="n"/>
+      <c r="C19" s="91" t="n"/>
+      <c r="D19" s="91" t="n"/>
+      <c r="E19" s="91" t="n"/>
+      <c r="F19" s="91" t="n"/>
+      <c r="G19" s="91" t="n"/>
+      <c r="H19" s="92" t="n"/>
     </row>
     <row r="20" ht="25" customHeight="1">
       <c r="A20" s="76" t="inlineStr">
@@ -5861,13 +5958,13 @@
           <t>■ グループ割り振り詳細</t>
         </is>
       </c>
-      <c r="B28" s="71" t="n"/>
-      <c r="C28" s="71" t="n"/>
-      <c r="D28" s="71" t="n"/>
-      <c r="E28" s="71" t="n"/>
-      <c r="F28" s="71" t="n"/>
-      <c r="G28" s="71" t="n"/>
-      <c r="H28" s="71" t="n"/>
+      <c r="B28" s="91" t="n"/>
+      <c r="C28" s="91" t="n"/>
+      <c r="D28" s="91" t="n"/>
+      <c r="E28" s="91" t="n"/>
+      <c r="F28" s="91" t="n"/>
+      <c r="G28" s="91" t="n"/>
+      <c r="H28" s="92" t="n"/>
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="76" t="inlineStr">
@@ -5995,13 +6092,13 @@
           <t>■ 成功させるための5つのポイント</t>
         </is>
       </c>
-      <c r="B32" s="71" t="n"/>
-      <c r="C32" s="71" t="n"/>
-      <c r="D32" s="71" t="n"/>
-      <c r="E32" s="71" t="n"/>
-      <c r="F32" s="71" t="n"/>
-      <c r="G32" s="71" t="n"/>
-      <c r="H32" s="71" t="n"/>
+      <c r="B32" s="91" t="n"/>
+      <c r="C32" s="91" t="n"/>
+      <c r="D32" s="91" t="n"/>
+      <c r="E32" s="91" t="n"/>
+      <c r="F32" s="91" t="n"/>
+      <c r="G32" s="91" t="n"/>
+      <c r="H32" s="92" t="n"/>
     </row>
     <row r="33" ht="40" customHeight="1">
       <c r="A33" s="80" t="inlineStr">
@@ -6009,17 +6106,17 @@
           <t>✔ カメラON徹底</t>
         </is>
       </c>
-      <c r="B33" s="71" t="n"/>
+      <c r="B33" s="92" t="n"/>
       <c r="C33" s="77" t="inlineStr">
         <is>
           <t>事前メールに「交流が目的なのでカメラONでご参加ください」と明記。当日冒頭でも笑顔でお願いする。</t>
         </is>
       </c>
-      <c r="D33" s="71" t="n"/>
-      <c r="E33" s="71" t="n"/>
-      <c r="F33" s="71" t="n"/>
-      <c r="G33" s="71" t="n"/>
-      <c r="H33" s="71" t="n"/>
+      <c r="D33" s="91" t="n"/>
+      <c r="E33" s="91" t="n"/>
+      <c r="F33" s="91" t="n"/>
+      <c r="G33" s="91" t="n"/>
+      <c r="H33" s="92" t="n"/>
     </row>
     <row r="34" ht="40" customHeight="1">
       <c r="A34" s="80" t="inlineStr">
@@ -6027,17 +6124,17 @@
           <t>✔ 人事が一番楽しむ</t>
         </is>
       </c>
-      <c r="B34" s="71" t="n"/>
+      <c r="B34" s="92" t="n"/>
       <c r="C34" s="77" t="inlineStr">
         <is>
           <t>人事担当者がテンション1.2倍。予想ゲームでも「私も予想します！」と参加すると場が温まる。</t>
         </is>
       </c>
-      <c r="D34" s="71" t="n"/>
-      <c r="E34" s="71" t="n"/>
-      <c r="F34" s="71" t="n"/>
-      <c r="G34" s="71" t="n"/>
-      <c r="H34" s="71" t="n"/>
+      <c r="D34" s="91" t="n"/>
+      <c r="E34" s="91" t="n"/>
+      <c r="F34" s="91" t="n"/>
+      <c r="G34" s="91" t="n"/>
+      <c r="H34" s="92" t="n"/>
     </row>
     <row r="35" ht="40" customHeight="1">
       <c r="A35" s="80" t="inlineStr">
@@ -6045,17 +6142,17 @@
           <t>✔ 問題を事前にカスタマイズ</t>
         </is>
       </c>
-      <c r="B35" s="71" t="n"/>
+      <c r="B35" s="92" t="n"/>
       <c r="C35" s="77" t="inlineStr">
         <is>
           <t>内定承諾者のプロフィール（スポーツ経験・出身地・バイト）を見て問題をカスタマイズすると「これ私のこと知ってる？」という驚きと笑いが生まれる。</t>
         </is>
       </c>
-      <c r="D35" s="71" t="n"/>
-      <c r="E35" s="71" t="n"/>
-      <c r="F35" s="71" t="n"/>
-      <c r="G35" s="71" t="n"/>
-      <c r="H35" s="71" t="n"/>
+      <c r="D35" s="91" t="n"/>
+      <c r="E35" s="91" t="n"/>
+      <c r="F35" s="91" t="n"/>
+      <c r="G35" s="91" t="n"/>
+      <c r="H35" s="92" t="n"/>
     </row>
     <row r="36" ht="40" customHeight="1">
       <c r="A36" s="80" t="inlineStr">
@@ -6063,17 +6160,17 @@
           <t>✔ 会社説明の5分を厳守</t>
         </is>
       </c>
-      <c r="B36" s="71" t="n"/>
+      <c r="B36" s="92" t="n"/>
       <c r="C36" s="77" t="inlineStr">
         <is>
           <t>「答えはまだわからない」宙ぶらりん感が後半への期待を作る。会社説明が長引くとその効果が消える。5分を必ず守る。</t>
         </is>
       </c>
-      <c r="D36" s="71" t="n"/>
-      <c r="E36" s="71" t="n"/>
-      <c r="F36" s="71" t="n"/>
-      <c r="G36" s="71" t="n"/>
-      <c r="H36" s="71" t="n"/>
+      <c r="D36" s="91" t="n"/>
+      <c r="E36" s="91" t="n"/>
+      <c r="F36" s="91" t="n"/>
+      <c r="G36" s="91" t="n"/>
+      <c r="H36" s="92" t="n"/>
     </row>
     <row r="37" ht="40" customHeight="1">
       <c r="A37" s="80" t="inlineStr">
@@ -6081,17 +6178,17 @@
           <t>✔ エピソードの深掘りが鍵</t>
         </is>
       </c>
-      <c r="B37" s="71" t="n"/>
+      <c r="B37" s="92" t="n"/>
       <c r="C37" s="77" t="inlineStr">
         <is>
           <t>答え合わせで手を挙げた人に「どんな経緯で？」と一言聞くだけで場が温まる。深掘りの質を人事が担うことで会話の密度が上がる。</t>
         </is>
       </c>
-      <c r="D37" s="71" t="n"/>
-      <c r="E37" s="71" t="n"/>
-      <c r="F37" s="71" t="n"/>
-      <c r="G37" s="71" t="n"/>
-      <c r="H37" s="71" t="n"/>
+      <c r="D37" s="91" t="n"/>
+      <c r="E37" s="91" t="n"/>
+      <c r="F37" s="91" t="n"/>
+      <c r="G37" s="91" t="n"/>
+      <c r="H37" s="92" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="22">
@@ -6105,8 +6202,8 @@
     <mergeCell ref="A33:B33"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="C37:H37"/>
+    <mergeCell ref="A5:H5"/>
     <mergeCell ref="C34:H34"/>
-    <mergeCell ref="A5:H5"/>
     <mergeCell ref="A32:H32"/>
     <mergeCell ref="A8:H8"/>
     <mergeCell ref="A35:B35"/>
@@ -6120,4 +6217,887 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="107" t="inlineStr">
+        <is>
+          <t>27新卒 内定承諾者向け 顔合わせ企画書（Zoom・60分）　【構成改訂版 v4】</t>
+        </is>
+      </c>
+      <c r="B1" s="108" t="n"/>
+      <c r="C1" s="108" t="n"/>
+      <c r="D1" s="108" t="n"/>
+      <c r="E1" s="108" t="n"/>
+      <c r="F1" s="108" t="n"/>
+      <c r="G1" s="108" t="n"/>
+      <c r="H1" s="108" t="n"/>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="109" t="inlineStr">
+        <is>
+          <t>参加者：内定承諾者 各グループ ＋ 人事担当　／　形式：Zoom　／　総時間：55〜60分</t>
+        </is>
+      </c>
+      <c r="B2" s="110" t="n"/>
+      <c r="C2" s="110" t="n"/>
+      <c r="D2" s="110" t="n"/>
+      <c r="E2" s="110" t="n"/>
+      <c r="F2" s="110" t="n"/>
+      <c r="G2" s="110" t="n"/>
+      <c r="H2" s="110" t="n"/>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="111" t="inlineStr">
+        <is>
+          <t>■ 設計思想・構成の原則</t>
+        </is>
+      </c>
+      <c r="B3" s="108" t="n"/>
+      <c r="C3" s="108" t="n"/>
+      <c r="D3" s="108" t="n"/>
+      <c r="E3" s="108" t="n"/>
+      <c r="F3" s="108" t="n"/>
+      <c r="G3" s="108" t="n"/>
+      <c r="H3" s="108" t="n"/>
+    </row>
+    <row r="4" ht="95" customHeight="1">
+      <c r="A4" s="109" t="inlineStr">
+        <is>
+          <t>【構成の原則】
+アイスブレイク（自己紹介） → 【ワーク前半】グループ内で共通点を探す → 会社説明（休憩がてら・5分） → 【ワーク後半】全体への発表・深掘り → クロージング
+【前半・後半のつながり】
+前半と後半は「共通点探し」という同一ワークの中の"準備フェーズ"と"発表フェーズ"。
+前半でグループ内の会話を通じて共通点を深掘りし、後半でそれを全体に発表することで「グループの個性」が見えて盛り上がる。
+会社説明は前半の盛り上がりの直後に「息継ぎ」として差し込む。アウトプットを求めず5分で完結させる。</t>
+        </is>
+      </c>
+      <c r="B4" s="110" t="n"/>
+      <c r="C4" s="110" t="n"/>
+      <c r="D4" s="110" t="n"/>
+      <c r="E4" s="110" t="n"/>
+      <c r="F4" s="110" t="n"/>
+      <c r="G4" s="110" t="n"/>
+      <c r="H4" s="110" t="n"/>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="111" t="inlineStr">
+        <is>
+          <t>■ 全体タイムライン</t>
+        </is>
+      </c>
+      <c r="B5" s="108" t="n"/>
+      <c r="C5" s="108" t="n"/>
+      <c r="D5" s="108" t="n"/>
+      <c r="E5" s="108" t="n"/>
+      <c r="F5" s="108" t="n"/>
+      <c r="G5" s="108" t="n"/>
+      <c r="H5" s="108" t="n"/>
+    </row>
+    <row r="6" ht="52" customHeight="1">
+      <c r="A6" s="112" t="inlineStr">
+        <is>
+          <t>0〜5分
+流れ説明
++人事自己紹介</t>
+        </is>
+      </c>
+      <c r="B6" s="112" t="inlineStr">
+        <is>
+          <t>5〜15分
+アイスブレイク
+自己紹介リレー</t>
+        </is>
+      </c>
+      <c r="C6" s="113" t="inlineStr">
+        <is>
+          <t>15〜30分
+【ワーク前半】
+グループ内
+共通点探し</t>
+        </is>
+      </c>
+      <c r="D6" s="112" t="inlineStr">
+        <is>
+          <t>30〜35分
+会社説明
+（休憩がてら）</t>
+        </is>
+      </c>
+      <c r="E6" s="113" t="inlineStr">
+        <is>
+          <t>35〜55分
+【ワーク後半】
+全体発表・
+深掘りトーク</t>
+        </is>
+      </c>
+      <c r="F6" s="112" t="inlineStr">
+        <is>
+          <t>55〜60分
+クロージング
+次回予告</t>
+        </is>
+      </c>
+      <c r="H6" s="114" t="n"/>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="114" t="n"/>
+      <c r="B7" s="114" t="n"/>
+      <c r="C7" s="115" t="inlineStr">
+        <is>
+          <t>◀━━━ 同一ワーク「共通点探し」　前半＝グループ内で探す　/　後半＝全体に発表 ━━━▶</t>
+        </is>
+      </c>
+      <c r="D7" s="110" t="n"/>
+      <c r="E7" s="110" t="n"/>
+      <c r="F7" s="114" t="n"/>
+      <c r="G7" s="114" t="n"/>
+      <c r="H7" s="114" t="n"/>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="111" t="inlineStr">
+        <is>
+          <t>■ プログラム詳細</t>
+        </is>
+      </c>
+      <c r="B8" s="108" t="n"/>
+      <c r="C8" s="108" t="n"/>
+      <c r="D8" s="108" t="n"/>
+      <c r="E8" s="108" t="n"/>
+      <c r="F8" s="108" t="n"/>
+      <c r="G8" s="108" t="n"/>
+      <c r="H8" s="108" t="n"/>
+    </row>
+    <row r="9" ht="35" customHeight="1">
+      <c r="A9" s="116" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B9" s="116" t="inlineStr">
+        <is>
+          <t>コンテンツ名</t>
+        </is>
+      </c>
+      <c r="C9" s="116" t="inlineStr">
+        <is>
+          <t>時間
+（累計）</t>
+        </is>
+      </c>
+      <c r="D9" s="116" t="inlineStr">
+        <is>
+          <t>狙い（Why）</t>
+        </is>
+      </c>
+      <c r="E9" s="116" t="inlineStr">
+        <is>
+          <t>進行スクリプト（How）
+※かぎ括弧がそのまま使えるセリフ例</t>
+        </is>
+      </c>
+      <c r="F9" s="116" t="inlineStr">
+        <is>
+          <t>成功の判断基準</t>
+        </is>
+      </c>
+      <c r="G9" s="116" t="inlineStr">
+        <is>
+          <t>リスクと対策</t>
+        </is>
+      </c>
+      <c r="H9" s="116" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="130" customHeight="1">
+      <c r="A10" s="117" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B10" s="118" t="inlineStr">
+        <is>
+          <t>入室待機
+・BGM</t>
+        </is>
+      </c>
+      <c r="C10" s="117" t="inlineStr">
+        <is>
+          <t>開始15分前
+（待機）</t>
+        </is>
+      </c>
+      <c r="D10" s="117" t="inlineStr">
+        <is>
+          <t>「この会社はちゃんとしている」という第一印象を開始前から形成する。緊張状態で入室する学生の不安を事前に下げる。</t>
+        </is>
+      </c>
+      <c r="E10" s="117" t="inlineStr">
+        <is>
+          <t>【準備チェックリスト】
+□ BGMを流す（Spotifyリラックス系推奨）
+□ 待機画面に「今日の流れ」スライドを表示
+□ チャットに「こんにちは！今日はよろしくお願いします😊 カメラONにしてもらえると嬉しいです！」を準備
+□ MC担当 / チャット＆タイム管理担当の役割確認
+【入室時の声かけ例】
+「〇〇さん、入ってくれましたね！今日はよろしくお願いします。全員揃うまで気楽にしていてください」</t>
+        </is>
+      </c>
+      <c r="F10" s="117" t="inlineStr">
+        <is>
+          <t>全員カメラON・笑顔で入室</t>
+        </is>
+      </c>
+      <c r="G10" s="117" t="inlineStr">
+        <is>
+          <t>無言入室が続く場合 → 個人名で「〇〇さん、今日どこから参加ですか？」と話しかける</t>
+        </is>
+      </c>
+      <c r="H10" s="117" t="inlineStr">
+        <is>
+          <t>開始5分前にリマインドをチャットで送る</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="130" customHeight="1">
+      <c r="A11" s="119" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B11" s="120" t="inlineStr">
+        <is>
+          <t>流れ説明
+＋人事自己紹介</t>
+        </is>
+      </c>
+      <c r="C11" s="119" t="inlineStr">
+        <is>
+          <t>0〜5分
+（5分）</t>
+        </is>
+      </c>
+      <c r="D11" s="119" t="inlineStr">
+        <is>
+          <t>①ゴールを2つに絞って言語化することで参加者の心理的ハードルを下げる。②人事が先に自己開示することで「この場では自己開示してよい」という規範を示す（モデリング効果）。</t>
+        </is>
+      </c>
+      <c r="E11" s="119" t="inlineStr">
+        <is>
+          <t>【冒頭セリフ例（そのまま使用可）】
+「みなさん、こんにちは！今日は最初の顔合わせということでとても楽しみにしてきました。
+今日のゴールは2つだけ。①全員の顔と名前を覚える。②今日楽しかった、と思いながら画面を閉じる。それだけです！
+今日はグループワークもありますので、ぜひ楽しんでいってください。まず私から自己紹介しますね。」
+【人事自己紹介の構成（60秒）】
+① 名前・担当業務（10秒）
+② 今ハマっていること・推し（具体的に、20秒）
+③ 意外な一面・ギャップ（20秒）
+④ 「今日は皆さんのことをもっと知りたくてきました！」（10秒）</t>
+        </is>
+      </c>
+      <c r="F11" s="119" t="inlineStr">
+        <is>
+          <t>参加者が笑顔でうなずいている・チャットでリアクションがある</t>
+        </is>
+      </c>
+      <c r="G11" s="119" t="inlineStr">
+        <is>
+          <t>人事が緊張して棒読みになる → 必ず前日にリハーサルを実施する</t>
+        </is>
+      </c>
+      <c r="H11" s="119" t="inlineStr">
+        <is>
+          <t>スライド1枚：今日の流れ図を画面共有</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="130" customHeight="1">
+      <c r="A12" s="117" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B12" s="118" t="inlineStr">
+        <is>
+          <t>1分自己紹介
+リレー
+（アイスブレイク）</t>
+        </is>
+      </c>
+      <c r="C12" s="117" t="inlineStr">
+        <is>
+          <t>5〜15分
+（10分）</t>
+        </is>
+      </c>
+      <c r="D12" s="117" t="inlineStr">
+        <is>
+          <t>顔・名前・キャラクターを一致させる。後半の共通点探しで「あの人は〇〇だから共通点になる」と話が繋がるための情報を全員で共有する場でもある。指名形式で全員が必ず1度発言する。</t>
+        </is>
+      </c>
+      <c r="E12" s="117" t="inlineStr">
+        <is>
+          <t>【項目（画面共有で表示）】
+① 名前・大学
+② 最近の推し or マイブーム（何でもOK）→ 可能なら画面に映す
+③ 一言キャッチフレーズ（例："見た目は地味ですが熱量だけはあります"）
+【進行セリフ例】
+「自己紹介をしていきます。推しは何でもOK！最後に次の人を指名してバトンを渡してください。
+後でグループワークがあるので、みなさんの話をよく覚えておいてください（笑）。では〇〇さんからお願いします！」
+【チャット担当の動き（重要）】
+各発言に対してリアルタイムで反応を流す
+例：「〇〇大学！いいですね」「推し、わかります笑」
+→ スタンプ（拍手・ハート）を積極的に使う
+【参加者プロフィール活用（事前確認）】
+・富川（野球全国優勝）→「え、全国⁉」でチャットが沸く。早めに登場させる
+・折笠（甲子園チア部優勝・学祭委員長80名）→ 発表慣れあり。グループワークでもリード役になる
+・本多（キックボクシング）→「え、格闘技⁉」で場が盛り上がる
+・佐々木（評価1位・録音→ロープレ繰り返し）→「努力の天才」キャラとして紹介できる</t>
+        </is>
+      </c>
+      <c r="F12" s="117" t="inlineStr">
+        <is>
+          <t>全員が1回は笑いを取れている・チャットが賑わっている</t>
+        </is>
+      </c>
+      <c r="G12" s="117" t="inlineStr">
+        <is>
+          <t>一人が長くなる → 「いいですね！じゃあ次の方にバトンを」と自然に促す</t>
+        </is>
+      </c>
+      <c r="H12" s="117" t="inlineStr">
+        <is>
+          <t>事前に推しが分かるものを画面に映すよう案内</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="130" customHeight="1">
+      <c r="A13" s="119" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B13" s="120" t="inlineStr">
+        <is>
+          <t>【ワーク前半】
+共通点探し
+（グループ内）</t>
+        </is>
+      </c>
+      <c r="C13" s="119" t="inlineStr">
+        <is>
+          <t>15〜30分
+（15分）</t>
+        </is>
+      </c>
+      <c r="D13" s="119" t="inlineStr">
+        <is>
+          <t>自己開示を通じて「意外な共通点」を発見することで親近感が生まれる（類似性の法則）。
+グループ内で会話しながら共通点を掘り起こす体験が「一緒に何かをした」という連帯感をつくる。
+この段階では全体発表せず"ネタをストックする"フェーズに徹することで、後半発表への期待感を生む。</t>
+        </is>
+      </c>
+      <c r="E13" s="119" t="inlineStr">
+        <is>
+          <t>【ルール（画面共有で表示）】
+① 15分間でできるだけ多くの共通点を見つける
+② 当たり前すぎる共通点は禁止（大学生・服を着ている・スマホを持っている 等）
+③ 深い共通点ほど価値が高い（"日本人" &lt; "小学校で途中で習い事を辞めた経験がある"）
+④ 後半で全体に発表するので、面白いエピソードつきの共通点を優先してメモしておく
+【進行セリフ例】
+「では共通点探しゲームをやります！グループで15分間、できるだけ多くの共通点を見つけてください。
+自己紹介で話したこと以外でOK。趣味・好きな食べ物・苦手なこと・子どもの頃の話など何でも。
+"当たり前すぎる禁止"です。後半でみんなの前に発表しますので、面白い共通点を重点的に集めてください！じゃあスタート！」
+【14分経過時の声かけ】
+「あと1分！発表する共通点、3つに絞っておいてください！」
+【会社説明への橋渡しセリフ（重要）】
+「探せましたか！？発表は後でじっくりやります。ここで少しだけ脳を休めて、弊社のことを3分でお伝えしますね。"少しだけ"なので安心してください（笑）」</t>
+        </is>
+      </c>
+      <c r="F13" s="119" t="inlineStr">
+        <is>
+          <t>各グループで活発に会話が起きている・「それ私も！」という声が出ている</t>
+        </is>
+      </c>
+      <c r="G13" s="119" t="inlineStr">
+        <is>
+          <t>会話が停滞した場合 → 人事が「〇〇さんと△△さんって出身地近かったりします？」など橋渡しをする</t>
+        </is>
+      </c>
+      <c r="H13" s="119" t="inlineStr">
+        <is>
+          <t>6/23（女子4名）は1グループ全員で実施。6/30（混合6名）は2〜3名のブレイクアウトルームに分けてもよい</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="130" customHeight="1">
+      <c r="A14" s="117" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B14" s="118" t="inlineStr">
+        <is>
+          <t>会社説明
+（休憩がてら
+インプットのみ）</t>
+        </is>
+      </c>
+      <c r="C14" s="117" t="inlineStr">
+        <is>
+          <t>30〜35分
+（5分）</t>
+        </is>
+      </c>
+      <c r="D14" s="117" t="inlineStr">
+        <is>
+          <t>盛り上がったワーク前半の直後に「自然な息継ぎ」として差し込む。アウトプットは一切求めない。3つのキーワードを記憶に残すだけでよい。「後半の発表が残っている」という状態が、学生を会社説明中も前のめりな状態に保つ。</t>
+        </is>
+      </c>
+      <c r="E14" s="117" t="inlineStr">
+        <is>
+          <t>【冒頭セリフ（警戒させないための言い回し）】
+「少しだけ弊社のことをお伝えさせてください。まだあまり知らない状態で入社するのも不安だと思うので、改めて簡単にご紹介します。3分だけお付き合いください！」
+【伝える3点（各1分・計3分）】
+① 業界NO.1の安定性
+「人材派遣業界の中でも建設・インフラ特化で業界シェアトップクラスです。建設インフラは社会インフラそのものなので景気に左右されにくい特性があります。」
+② 本社勤め・選ぶ側
+「皆さんは派遣される側ではなく、派遣する側・コーディネートする側です。毎日スーツで本社出社が基本で、現場仕事ではありません。」
+③ 大手グループの安定感
+「〇〇グループ傘下として、バックアップ体制もしっかりしています。」
+【締めセリフ（後半発表へのつなぎ）】
+「友達や親御さんに"どんな会社？"と聞かれたときこの3つを話すだけで説明になります。覚えておいてくださいね。
+では、お待ちかねの発表に移りましょう！みなさんのグループからどんな共通点が出てきたか楽しみです！」</t>
+        </is>
+      </c>
+      <c r="F14" s="117" t="inlineStr">
+        <is>
+          <t>ネガティブな反応が出ていない・参加者がうなずいている</t>
+        </is>
+      </c>
+      <c r="G14" s="117" t="inlineStr">
+        <is>
+          <t>説明が長くなる → 必ず5分で切る。詳細は後日メールで補足
+暗い雰囲気になる → 「発表が楽しみ」という言葉で後半への期待感をつくる</t>
+        </is>
+      </c>
+      <c r="H14" s="117" t="inlineStr">
+        <is>
+          <t>説明会資料から該当スライドを最大3枚に絞る</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="130" customHeight="1">
+      <c r="A15" s="119" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B15" s="120" t="inlineStr">
+        <is>
+          <t>【ワーク後半】
+共通点発表
+＋深掘りトーク
+（全体）</t>
+        </is>
+      </c>
+      <c r="C15" s="119" t="inlineStr">
+        <is>
+          <t>35〜55分
+（20分）</t>
+        </is>
+      </c>
+      <c r="D15" s="119" t="inlineStr">
+        <is>
+          <t>前半でグループ内に蓄積された「共通点ネタ」を全体に発表することで、グループをまたいだ共通点発見や驚きが生まれる。
+発表後に深掘りトークを入れることで一人ひとりのキャラクターがより鮮明になり「この人に話しかけてみたい」という気持ちが生まれる。
+前半の「探す体験」と後半の「発表する体験」が組み合わさることで達成感と一体感が同時に生まれる。</t>
+        </is>
+      </c>
+      <c r="E15" s="119" t="inlineStr">
+        <is>
+          <t>【発表フェーズ（各グループ3〜4分 × 2〜3グループ ＝ 約10〜12分）】
+【進行セリフ例】
+「では発表タイムです！各グループから自慢の共通点を教えてください。面白いやつ、意外なやつ優先でどうぞ！
+まず〇〇グループからお願いします！」
+【発表中の人事の動き（チャット担当と連携）】
+・各発表に対して「それ、すごく意外！」「え、〇〇グループにもいる？」と声で反応する
+・チャット担当は発表内容に対して「同じ！」「わかる！」などを流す
+・グループをまたいだ共通点が出たら「他のグループも同じ人いますか？」と全体に振る
+【深掘りトーク（各グループ発表後 or 気になったネタに対して）】
+・「それって具体的にどういうこと？」「いつ気づいたんですか？」
+・「〇〇さんの場合はどうだったんですか？」と個人に深掘りを振る
+【全グループ発表後：全体共通点ランキング発表（約5〜8分）】
+「全部聞いてみて、全グループに共通していた共通点を発表します！」
+→ 人事が発表を聞きながらリアルタイムでメモした全体共通点を3つ発表
+→ 「これは〇〇さんと△△さんが言っていた共通点ですね、実は全員に当てはまりました！」
+【締めセリフ（クロージングへの橋渡し）】
+「いや〜、みんな意外なところで繋がっていましたね！今日だけで〇〇という共通点が見つかったのが一番驚きました（笑）」</t>
+        </is>
+      </c>
+      <c r="F15" s="119" t="inlineStr">
+        <is>
+          <t>各グループが3つ以上の共通点を発表できている・発表に対して笑いや驚きの反応が複数回起きている</t>
+        </is>
+      </c>
+      <c r="G15" s="119" t="inlineStr">
+        <is>
+          <t>発表が単調になる → 人事が「それ、深掘りしてもいいですか？」と介入する
+時間が余る → 全体共通点ランキングの解説を丁寧にする
+時間が足りない → 全体共通点ランキングを省略して各グループ発表を優先</t>
+        </is>
+      </c>
+      <c r="H15" s="119" t="inlineStr">
+        <is>
+          <t>6/23（女子4名）は1グループのみなので発表に十分時間をかけて深掘りトークを充実させる
+6/30（混合6名）は2グループに分けて発表し合う形式にすると盛り上がりやすい</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="130" customHeight="1">
+      <c r="A16" s="117" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B16" s="118" t="inlineStr">
+        <is>
+          <t>クロージング
+＋次回予告</t>
+        </is>
+      </c>
+      <c r="C16" s="117" t="inlineStr">
+        <is>
+          <t>55〜60分
+（5分）</t>
+        </is>
+      </c>
+      <c r="D16" s="117" t="inlineStr">
+        <is>
+          <t>「またこのメンバーに会いたい」という感情で終わらせる。次のイベントへの期待値を上げ入社までの緩やかなつながりを維持する。アンケートで本音を収集し次回以降に活かす。</t>
+        </is>
+      </c>
+      <c r="E16" s="117" t="inlineStr">
+        <is>
+          <t>【締めセリフ例（そのまま使用可）】
+「今日はありがとうございました！最初はどんな会話になるか少し緊張していたんですが、みなさんのおかげでとても盛り上がりましたね。
+今日だけで〇〇という共通点が見つかったり、△△さんの意外な一面が見えたり、一気に仲間感が出た気がしています。
+次は〇月〇日に対面での顔合わせを予定しています。今度は直接会えるのが楽しみです！
+それまでも何かあれば遠慮なく私に連絡してください。連絡先はチャットに貼りますね。
+では最後にアンケートだけお願いします。1分で終わります！URLをチャットに貼ります。」
+【チャットに貼るもの（事前にコピー準備）】
+□ アンケートフォームURL
+□ 次回日程（テキスト）
+□ 人事担当の連絡先（LINE or メール）
+【アンケート項目（5問・1分以内）】
+① 今日の満足度（5段階）
+② 一番楽しかったコンテンツ（選択式）
+③ 入社に対して不安に思っていることがあれば（自由記述・任意）
+④ 次回も参加したいと思えましたか（Yes/No）
+⑤ 一言感想（任意）</t>
+        </is>
+      </c>
+      <c r="F16" s="117" t="inlineStr">
+        <is>
+          <t>参加者全員がアンケートを送信・次回日程をスケジュール登録</t>
+        </is>
+      </c>
+      <c r="G16" s="117" t="inlineStr">
+        <is>
+          <t>時間オーバーの場合 → 全体共通点ランキングを省略する。クロージング時間は絶対に削らない</t>
+        </is>
+      </c>
+      <c r="H16" s="117" t="inlineStr">
+        <is>
+          <t>クロージング後に5〜10分の任意雑談タイムを設けると帰属意識が上がる</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="111" t="inlineStr">
+        <is>
+          <t>■ グループ割り振り詳細</t>
+        </is>
+      </c>
+      <c r="B17" s="108" t="n"/>
+      <c r="C17" s="108" t="n"/>
+      <c r="D17" s="108" t="n"/>
+      <c r="E17" s="108" t="n"/>
+      <c r="F17" s="108" t="n"/>
+      <c r="G17" s="108" t="n"/>
+      <c r="H17" s="108" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="116" t="inlineStr">
+        <is>
+          <t>日程</t>
+        </is>
+      </c>
+      <c r="B18" s="116" t="inlineStr">
+        <is>
+          <t>規模・構成</t>
+        </is>
+      </c>
+      <c r="C18" s="116" t="inlineStr">
+        <is>
+          <t>参加者</t>
+        </is>
+      </c>
+      <c r="D18" s="116" t="inlineStr">
+        <is>
+          <t>ワーク進行のポイント</t>
+        </is>
+      </c>
+      <c r="E18" s="116" t="inlineStr">
+        <is>
+          <t>担当人事</t>
+        </is>
+      </c>
+      <c r="F18" s="116" t="inlineStr">
+        <is>
+          <t>特記事項</t>
+        </is>
+      </c>
+      <c r="G18" s="116" t="inlineStr"/>
+      <c r="H18" s="116" t="inlineStr"/>
+    </row>
+    <row r="19" ht="90" customHeight="1">
+      <c r="A19" s="120" t="inlineStr">
+        <is>
+          <t>2026/6/23
+11:00〜12:00</t>
+        </is>
+      </c>
+      <c r="B19" s="119" t="inlineStr">
+        <is>
+          <t>4名
+女性のみ</t>
+        </is>
+      </c>
+      <c r="C19" s="119" t="inlineStr">
+        <is>
+          <t>市川 結菜（神奈川大学）
+柳澤 明（東京経済大学）
+荒井 翠（駒澤大学）
+根本 彩花（東京富士大学）</t>
+        </is>
+      </c>
+      <c r="D19" s="119" t="inlineStr">
+        <is>
+          <t>【前半】1グループ全員で共通点を探す。少人数なので深掘りしやすい。共通点の"質"を重視。
+【後半】全体発表は1グループのみなので、共通点ごとにエピソードを丁寧に話してもらう。深掘りトークに十分時間をかける。
+【市川】まとめ役 → 発表時のリード役に自然になる
+【荒井】ホスピタリティ高め → 他者を引き出す質問が得意</t>
+        </is>
+      </c>
+      <c r="E19" s="119" t="inlineStr">
+        <is>
+          <t>齋藤（MC）
+もう1名（チャット管理）</t>
+        </is>
+      </c>
+      <c r="F19" s="119" t="inlineStr">
+        <is>
+          <t>全員女性のため共感ベースの会話になりやすい。エピソードの深掘りを積極的に行う。</t>
+        </is>
+      </c>
+      <c r="G19" s="119" t="inlineStr"/>
+      <c r="H19" s="119" t="inlineStr"/>
+    </row>
+    <row r="20" ht="90" customHeight="1">
+      <c r="A20" s="118" t="inlineStr">
+        <is>
+          <t>2026/6/30
+15:00〜16:00</t>
+        </is>
+      </c>
+      <c r="B20" s="117" t="inlineStr">
+        <is>
+          <t>6名
+女3・男3</t>
+        </is>
+      </c>
+      <c r="C20" s="117" t="inlineStr">
+        <is>
+          <t>富川 哲太（大阪経済大学）
+西山 心町（東海大学）
+吉田 雅野（大東文化大学）
+折笠 未來美（仙台白百合女子大学）
+佐々木 七都（福岡大学）
+本多 諒（九州産業大学）</t>
+        </is>
+      </c>
+      <c r="D20" s="117" t="inlineStr">
+        <is>
+          <t>【前半】2〜3名のブレイクアウトルームに分けて共通点を探す。グループをまたいだ共通点が後半で盛り上がりやすい。
+【後半】グループごとに発表し合う。他グループの共通点に「うちも同じ！」が出たら全体で盛り上げる。
+【富川】野球全国優勝 → 自己紹介で場を沸かせる。グループ内でもムードメーカー
+【本多】ボクサー → 意外な共通点を持っている可能性大。発表で笑いが取れる</t>
+        </is>
+      </c>
+      <c r="E20" s="117" t="inlineStr">
+        <is>
+          <t>齋藤（MC）
+もう1名（チャット管理）</t>
+        </is>
+      </c>
+      <c r="F20" s="117" t="inlineStr">
+        <is>
+          <t>男女混合で共通点の意外性が出やすい。ブレイクアウト後の全体発表で他グループとの共通点を見つける流れにする。</t>
+        </is>
+      </c>
+      <c r="G20" s="117" t="inlineStr"/>
+      <c r="H20" s="117" t="inlineStr"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="111" t="inlineStr">
+        <is>
+          <t>■ 成功させるための5つのポイント</t>
+        </is>
+      </c>
+      <c r="B21" s="108" t="n"/>
+      <c r="C21" s="108" t="n"/>
+      <c r="D21" s="108" t="n"/>
+      <c r="E21" s="108" t="n"/>
+      <c r="F21" s="108" t="n"/>
+      <c r="G21" s="108" t="n"/>
+      <c r="H21" s="108" t="n"/>
+    </row>
+    <row r="22" ht="40" customHeight="1">
+      <c r="A22" s="121" t="inlineStr">
+        <is>
+          <t>✔ カメラON徹底</t>
+        </is>
+      </c>
+      <c r="B22" s="110" t="n"/>
+      <c r="C22" s="117" t="inlineStr">
+        <is>
+          <t>事前メールに「交流が目的なのでカメラONでご参加ください」と明記。当日冒頭でも笑顔でお願いする。強制感を出さず自然に促す。</t>
+        </is>
+      </c>
+      <c r="D22" s="110" t="n"/>
+      <c r="E22" s="110" t="n"/>
+      <c r="F22" s="110" t="n"/>
+      <c r="G22" s="110" t="n"/>
+      <c r="H22" s="110" t="n"/>
+    </row>
+    <row r="23" ht="40" customHeight="1">
+      <c r="A23" s="121" t="inlineStr">
+        <is>
+          <t>✔ 人事が一番楽しむ</t>
+        </is>
+      </c>
+      <c r="B23" s="110" t="n"/>
+      <c r="C23" s="117" t="inlineStr">
+        <is>
+          <t>人事担当者がテンション1.2倍・一番に自己開示する。共通点探しで「私もそれあります！」と積極的に参加すると場が温まる。</t>
+        </is>
+      </c>
+      <c r="D23" s="110" t="n"/>
+      <c r="E23" s="110" t="n"/>
+      <c r="F23" s="110" t="n"/>
+      <c r="G23" s="110" t="n"/>
+      <c r="H23" s="110" t="n"/>
+    </row>
+    <row r="24" ht="40" customHeight="1">
+      <c r="A24" s="121" t="inlineStr">
+        <is>
+          <t>✔ 発表での深掘りが鍵</t>
+        </is>
+      </c>
+      <c r="B24" s="110" t="n"/>
+      <c r="C24" s="117" t="inlineStr">
+        <is>
+          <t>後半の発表で「それって具体的にどういうこと？」と一言深掘りするだけで場の密度が上がる。人事が深掘りの質を担う。</t>
+        </is>
+      </c>
+      <c r="D24" s="110" t="n"/>
+      <c r="E24" s="110" t="n"/>
+      <c r="F24" s="110" t="n"/>
+      <c r="G24" s="110" t="n"/>
+      <c r="H24" s="110" t="n"/>
+    </row>
+    <row r="25" ht="40" customHeight="1">
+      <c r="A25" s="121" t="inlineStr">
+        <is>
+          <t>✔ 会社説明の5分を厳守</t>
+        </is>
+      </c>
+      <c r="B25" s="110" t="n"/>
+      <c r="C25" s="117" t="inlineStr">
+        <is>
+          <t>「後半の発表が残っている」という状態が参加者を前のめりにさせる。会社説明が長引くとその効果が消える。5分を必ず守る。</t>
+        </is>
+      </c>
+      <c r="D25" s="110" t="n"/>
+      <c r="E25" s="110" t="n"/>
+      <c r="F25" s="110" t="n"/>
+      <c r="G25" s="110" t="n"/>
+      <c r="H25" s="110" t="n"/>
+    </row>
+    <row r="26" ht="40" customHeight="1">
+      <c r="A26" s="121" t="inlineStr">
+        <is>
+          <t>✔ グループをまたいだ共通点を見逃さない</t>
+        </is>
+      </c>
+      <c r="B26" s="110" t="n"/>
+      <c r="C26" s="117" t="inlineStr">
+        <is>
+          <t>後半発表で他グループと共通する内容が出たら「他のグループも！？」と全体に振ることで一体感が生まれる。人事がリアルタイムでメモしておく。</t>
+        </is>
+      </c>
+      <c r="D26" s="110" t="n"/>
+      <c r="E26" s="110" t="n"/>
+      <c r="F26" s="110" t="n"/>
+      <c r="G26" s="110" t="n"/>
+      <c r="H26" s="110" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="19">
+    <mergeCell ref="C25:H25"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C22:H22"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C23:H23"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="C24:H24"/>
+    <mergeCell ref="C26:H26"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/6月顔合わせ企画書_改善版.xlsx
+++ b/6月顔合わせ企画書_改善版.xlsx
@@ -15,6 +15,7 @@
     <sheet name="【改善版v2】6月企画書" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="【改善版v3】6月企画書" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="【改善版v4】6月企画書" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="【改善版v5】6月企画書" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191028" fullCalcOnLoad="1"/>
@@ -360,7 +361,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="34">
+  <borders count="42">
     <border>
       <left/>
       <right/>
@@ -756,11 +757,99 @@
         <color rgb="00000000"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="00000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="00000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="00000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="00000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="122">
+  <cellXfs count="126">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1033,6 +1122,10 @@
     <xf numFmtId="0" fontId="29" fillId="17" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1787,6 +1880,890 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="107" t="inlineStr">
+        <is>
+          <t>27新卒 内定承諾者向け 顔合わせ企画書（Zoom・60分）　【構成改訂版 v5】</t>
+        </is>
+      </c>
+      <c r="B1" s="108" t="n"/>
+      <c r="C1" s="108" t="n"/>
+      <c r="D1" s="108" t="n"/>
+      <c r="E1" s="108" t="n"/>
+      <c r="F1" s="108" t="n"/>
+      <c r="G1" s="108" t="n"/>
+      <c r="H1" s="108" t="n"/>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="109" t="inlineStr">
+        <is>
+          <t>参加者：内定承諾者 各グループ ＋ 人事担当　／　形式：Zoom　／　総時間：55〜60分</t>
+        </is>
+      </c>
+      <c r="B2" s="110" t="n"/>
+      <c r="C2" s="110" t="n"/>
+      <c r="D2" s="110" t="n"/>
+      <c r="E2" s="110" t="n"/>
+      <c r="F2" s="110" t="n"/>
+      <c r="G2" s="110" t="n"/>
+      <c r="H2" s="110" t="n"/>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="111" t="inlineStr">
+        <is>
+          <t>■ 設計思想・構成の原則</t>
+        </is>
+      </c>
+      <c r="B3" s="108" t="n"/>
+      <c r="C3" s="108" t="n"/>
+      <c r="D3" s="108" t="n"/>
+      <c r="E3" s="108" t="n"/>
+      <c r="F3" s="108" t="n"/>
+      <c r="G3" s="108" t="n"/>
+      <c r="H3" s="108" t="n"/>
+    </row>
+    <row r="4" ht="100" customHeight="1">
+      <c r="A4" s="109" t="inlineStr">
+        <is>
+          <t>【v5の変更点】
+v4では「前半ワーク → 会社説明 → 後半ワーク」の順だったが、v5では会社説明をワーク終了後に移動。
+【変更の理由】
+・ワークで盛り上がり、参加者同士が打ち解けた状態のあとに会社説明を聞かせることで受け取られ方が変わる
+・「楽しかった」という感情が会社への好印象と結びつくタイミングで説明を差し込める（感情一致効果）
+・ワークの流れを途切れさせず、最後まで盛り上がった状態で完結させてから会社説明に移れる
+【新しい構成の原則】
+アイスブレイク（自己紹介） → 【ワーク前半】グループ内で共通点探し → 【ワーク後半】全体発表・深掘りトーク → 会社説明（インプットのみ） → クロージング</t>
+        </is>
+      </c>
+      <c r="B4" s="110" t="n"/>
+      <c r="C4" s="110" t="n"/>
+      <c r="D4" s="110" t="n"/>
+      <c r="E4" s="110" t="n"/>
+      <c r="F4" s="110" t="n"/>
+      <c r="G4" s="110" t="n"/>
+      <c r="H4" s="110" t="n"/>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="111" t="inlineStr">
+        <is>
+          <t>■ 全体タイムライン</t>
+        </is>
+      </c>
+      <c r="B5" s="108" t="n"/>
+      <c r="C5" s="108" t="n"/>
+      <c r="D5" s="108" t="n"/>
+      <c r="E5" s="108" t="n"/>
+      <c r="F5" s="108" t="n"/>
+      <c r="G5" s="108" t="n"/>
+      <c r="H5" s="108" t="n"/>
+    </row>
+    <row r="6" ht="52" customHeight="1">
+      <c r="A6" s="112" t="inlineStr">
+        <is>
+          <t>0〜5分
+流れ説明
++人事自己紹介</t>
+        </is>
+      </c>
+      <c r="B6" s="112" t="inlineStr">
+        <is>
+          <t>5〜15分
+アイスブレイク
+自己紹介リレー</t>
+        </is>
+      </c>
+      <c r="C6" s="113" t="inlineStr">
+        <is>
+          <t>15〜30分
+【ワーク前半】
+グループ内
+共通点探し</t>
+        </is>
+      </c>
+      <c r="D6" s="113" t="inlineStr">
+        <is>
+          <t>30〜50分
+【ワーク後半】
+全体発表・
+深掘りトーク</t>
+        </is>
+      </c>
+      <c r="E6" s="112" t="inlineStr">
+        <is>
+          <t>50〜55分
+会社説明
+（インプットのみ）</t>
+        </is>
+      </c>
+      <c r="F6" s="112" t="inlineStr">
+        <is>
+          <t>55〜60分
+クロージング
+次回予告</t>
+        </is>
+      </c>
+      <c r="H6" s="114" t="n"/>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="114" t="n"/>
+      <c r="B7" s="114" t="n"/>
+      <c r="C7" s="115" t="inlineStr">
+        <is>
+          <t>◀━━━ 同一ワーク「共通点探し」　前半＝グループ内 / 後半＝全体発表 ━━━▶</t>
+        </is>
+      </c>
+      <c r="D7" s="110" t="n"/>
+      <c r="E7" s="114" t="n"/>
+      <c r="F7" s="114" t="n"/>
+      <c r="G7" s="114" t="n"/>
+      <c r="H7" s="114" t="n"/>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="111" t="inlineStr">
+        <is>
+          <t>■ プログラム詳細</t>
+        </is>
+      </c>
+      <c r="B8" s="108" t="n"/>
+      <c r="C8" s="108" t="n"/>
+      <c r="D8" s="108" t="n"/>
+      <c r="E8" s="108" t="n"/>
+      <c r="F8" s="108" t="n"/>
+      <c r="G8" s="108" t="n"/>
+      <c r="H8" s="108" t="n"/>
+    </row>
+    <row r="9" ht="35" customHeight="1">
+      <c r="A9" s="116" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B9" s="116" t="inlineStr">
+        <is>
+          <t>コンテンツ名</t>
+        </is>
+      </c>
+      <c r="C9" s="116" t="inlineStr">
+        <is>
+          <t>時間
+（累計）</t>
+        </is>
+      </c>
+      <c r="D9" s="116" t="inlineStr">
+        <is>
+          <t>狙い（Why）</t>
+        </is>
+      </c>
+      <c r="E9" s="116" t="inlineStr">
+        <is>
+          <t>進行スクリプト（How）
+※かぎ括弧がそのまま使えるセリフ例</t>
+        </is>
+      </c>
+      <c r="F9" s="116" t="inlineStr">
+        <is>
+          <t>成功の判断基準</t>
+        </is>
+      </c>
+      <c r="G9" s="116" t="inlineStr">
+        <is>
+          <t>リスクと対策</t>
+        </is>
+      </c>
+      <c r="H9" s="116" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="130" customHeight="1">
+      <c r="A10" s="117" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B10" s="118" t="inlineStr">
+        <is>
+          <t>入室待機
+・BGM</t>
+        </is>
+      </c>
+      <c r="C10" s="117" t="inlineStr">
+        <is>
+          <t>開始15分前
+（待機）</t>
+        </is>
+      </c>
+      <c r="D10" s="117" t="inlineStr">
+        <is>
+          <t>「この会社はちゃんとしている」という第一印象を開始前から形成する。緊張状態で入室する学生の不安を事前に下げる。</t>
+        </is>
+      </c>
+      <c r="E10" s="117" t="inlineStr">
+        <is>
+          <t>【準備チェックリスト】
+□ BGMを流す（Spotifyリラックス系推奨）
+□ 待機画面に「今日の流れ」スライドを表示
+□ チャットに「こんにちは！今日はよろしくお願いします😊 カメラONにしてもらえると嬉しいです！」を準備
+□ MC担当 / チャット＆タイム管理担当の役割確認
+【入室時の声かけ例】
+「〇〇さん、入ってくれましたね！今日はよろしくお願いします。全員揃うまで気楽にしていてください」</t>
+        </is>
+      </c>
+      <c r="F10" s="117" t="inlineStr">
+        <is>
+          <t>全員カメラON・笑顔で入室</t>
+        </is>
+      </c>
+      <c r="G10" s="117" t="inlineStr">
+        <is>
+          <t>無言入室が続く場合 → 個人名で「〇〇さん、今日どこから参加ですか？」と話しかける</t>
+        </is>
+      </c>
+      <c r="H10" s="117" t="inlineStr">
+        <is>
+          <t>開始5分前にリマインドをチャットで送る</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="130" customHeight="1">
+      <c r="A11" s="119" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B11" s="120" t="inlineStr">
+        <is>
+          <t>流れ説明
+＋人事自己紹介</t>
+        </is>
+      </c>
+      <c r="C11" s="119" t="inlineStr">
+        <is>
+          <t>0〜5分
+（5分）</t>
+        </is>
+      </c>
+      <c r="D11" s="119" t="inlineStr">
+        <is>
+          <t>①ゴールを2つに絞って言語化することで参加者の心理的ハードルを下げる。②人事が先に自己開示することで「この場では自己開示してよい」という規範を示す（モデリング効果）。</t>
+        </is>
+      </c>
+      <c r="E11" s="119" t="inlineStr">
+        <is>
+          <t>【冒頭セリフ例（そのまま使用可）】
+「みなさん、こんにちは！今日は最初の顔合わせということでとても楽しみにしてきました。
+今日のゴールは2つだけ。①全員の顔と名前を覚える。②今日楽しかった、と思いながら画面を閉じる。それだけです！
+グループワークもありますので、ぜひ楽しんでいってください。まず私から自己紹介しますね。」
+【人事自己紹介の構成（60秒）】
+① 名前・担当業務（10秒）
+② 今ハマっていること・推し（具体的に、20秒）
+③ 意外な一面・ギャップ（20秒）
+④ 「今日は皆さんのことをもっと知りたくてきました！」（10秒）</t>
+        </is>
+      </c>
+      <c r="F11" s="119" t="inlineStr">
+        <is>
+          <t>参加者が笑顔でうなずいている・チャットでリアクションがある</t>
+        </is>
+      </c>
+      <c r="G11" s="119" t="inlineStr">
+        <is>
+          <t>人事が緊張して棒読みになる → 必ず前日にリハーサルを実施する</t>
+        </is>
+      </c>
+      <c r="H11" s="119" t="inlineStr">
+        <is>
+          <t>スライド1枚：今日の流れ図を画面共有</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="130" customHeight="1">
+      <c r="A12" s="117" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B12" s="118" t="inlineStr">
+        <is>
+          <t>1分自己紹介
+リレー
+（アイスブレイク）</t>
+        </is>
+      </c>
+      <c r="C12" s="117" t="inlineStr">
+        <is>
+          <t>5〜15分
+（10分）</t>
+        </is>
+      </c>
+      <c r="D12" s="117" t="inlineStr">
+        <is>
+          <t>顔・名前・キャラクターを一致させる。後半のワークで「あの人と共通点がありそう」と判断するための情報を全員で共有するフェーズでもある。指名形式で全員が必ず1度発言する。</t>
+        </is>
+      </c>
+      <c r="E12" s="117" t="inlineStr">
+        <is>
+          <t>【項目（画面共有で表示）】
+① 名前・大学
+② 最近の推し or マイブーム（何でもOK）→ 可能なら画面に映す
+③ 一言キャッチフレーズ（例："見た目は地味ですが熱量だけはあります"）
+【進行セリフ例】
+「自己紹介をしていきます。推しは何でもOK！最後に次の人を指名してバトンを渡してください。
+後でグループワークがあるので、みなさんのことをよく覚えておいてください（笑）。では〇〇さんからお願いします！」
+【チャット担当の動き（重要）】
+各発言に対してリアルタイムで反応を流す。スタンプ（拍手・ハート）を積極的に使う
+【参加者プロフィール活用（事前確認）】
+・富川（野球全国優勝）→「え、全国⁉」でチャットが沸く。早めに登場させる
+・折笠（甲子園チア部優勝・学祭委員長80名）→ 発表慣れあり。グループワークでもリード役になる
+・本多（キックボクシング）→「え、格闘技⁉」で場が盛り上がる
+・佐々木（評価1位・録音→ロープレ繰り返し）→「努力の天才」キャラとして紹介できる</t>
+        </is>
+      </c>
+      <c r="F12" s="117" t="inlineStr">
+        <is>
+          <t>全員が1回は笑いを取れている・チャットが賑わっている</t>
+        </is>
+      </c>
+      <c r="G12" s="117" t="inlineStr">
+        <is>
+          <t>一人が長くなる → 「いいですね！じゃあ次の方にバトンを」と自然に促す</t>
+        </is>
+      </c>
+      <c r="H12" s="117" t="inlineStr">
+        <is>
+          <t>事前に推しが分かるものを画面に映すよう案内</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="130" customHeight="1">
+      <c r="A13" s="119" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B13" s="120" t="inlineStr">
+        <is>
+          <t>【ワーク前半】
+共通点探し
+（グループ内）</t>
+        </is>
+      </c>
+      <c r="C13" s="119" t="inlineStr">
+        <is>
+          <t>15〜30分
+（15分）</t>
+        </is>
+      </c>
+      <c r="D13" s="119" t="inlineStr">
+        <is>
+          <t>自己開示を通じて「意外な共通点」を発見することで親近感が生まれる（類似性の法則）。
+グループ内で一緒に探す体験が「一緒に何かをした」という連帯感をつくる。
+この段階では全体発表せず"ネタをストックするフェーズ"に徹することで、後半の発表への期待感を生む。</t>
+        </is>
+      </c>
+      <c r="E13" s="119" t="inlineStr">
+        <is>
+          <t>【ルール（画面共有で表示）】
+① 15分間でできるだけ多くの共通点を見つける
+② 当たり前すぎる共通点は禁止（大学生・服を着ている・スマホを持っている 等）
+③ 深い共通点ほど価値が高い（"日本人" &lt; "小学校で習い事を途中で辞めた経験がある"）
+④ 後半で全体に発表するので、エピソードつきの面白い共通点を優先してメモしておく
+【進行セリフ例】
+「では共通点探しゲームをやります！グループで15分間、できるだけ多くの共通点を見つけてください。
+自己紹介で話したこと以外でOK。趣味・好きな食べ物・苦手なこと・子どもの頃の話など何でも。
+"当たり前すぎる禁止"です。後半でみんなの前に発表しますので、面白い共通点を重点的に集めてください！じゃあスタート！」
+【14分経過時の声かけ】
+「あと1分！発表する共通点、3つに絞っておいてください！」</t>
+        </is>
+      </c>
+      <c r="F13" s="119" t="inlineStr">
+        <is>
+          <t>各グループで活発に会話が起きている・「それ私も！」という声が出ている</t>
+        </is>
+      </c>
+      <c r="G13" s="119" t="inlineStr">
+        <is>
+          <t>会話が停滞した場合 → 人事が「〇〇さんと△△さんって出身地近かったりします？」など橋渡しをする</t>
+        </is>
+      </c>
+      <c r="H13" s="119" t="inlineStr">
+        <is>
+          <t>6/23（女子4名）は1グループ全員で実施。6/30（混合6名）は2〜3名のブレイクアウトルームに分けてもよい</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="130" customHeight="1">
+      <c r="A14" s="119" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B14" s="120" t="inlineStr">
+        <is>
+          <t>【ワーク後半】
+共通点発表
+＋深掘りトーク
+（全体）</t>
+        </is>
+      </c>
+      <c r="C14" s="119" t="inlineStr">
+        <is>
+          <t>30〜50分
+（20分）</t>
+        </is>
+      </c>
+      <c r="D14" s="119" t="inlineStr">
+        <is>
+          <t>前半でグループ内に蓄積された「共通点ネタ」を全体に発表することで、グループをまたいだ共通点発見や驚きが生まれる。
+発表後の深掘りトークで一人ひとりのキャラクターがより鮮明になり「この人に話しかけてみたい」という気持ちが生まれる。
+ワークが完全に完結した状態・最も盛り上がった状態のまま会社説明へ移行できる。</t>
+        </is>
+      </c>
+      <c r="E14" s="119" t="inlineStr">
+        <is>
+          <t>【発表フェーズ（各グループ3〜4分 × グループ数 ＝ 約10〜12分）】
+【進行セリフ例】
+「では発表タイムです！各グループから自慢の共通点を教えてください。面白いやつ、意外なやつ優先でどうぞ！
+まず〇〇グループからお願いします！」
+【発表中の人事の動き】
+・各発表に「それ、すごく意外！」「え、〇〇グループにもいる？」と声で反応する
+・チャット担当は「同じ！」「わかる！」などをリアルタイムで流す
+・グループをまたいだ共通点が出たら「他のグループも同じ人いますか？」と全体に振る
+【深掘りトーク（各グループ発表後 or 気になったネタに対して）】
+・「それって具体的にどういうこと？」「いつ気づいたんですか？」
+・「〇〇さんの場合はどうだったんですか？」と個人に深掘りを振る
+【全グループ発表後：全体共通点ランキング（約5〜8分）】
+「全部聞いてみて、全グループに共通していた共通点を発表します！」
+→ 人事がリアルタイムでメモした全体共通点を3つ発表
+→ 「これは〇〇さんと△△さんが言っていた共通点ですね、実は全員に当てはまりました！」
+【ワーク締めセリフ（会社説明への自然な橋渡し）】
+「いや〜、すごく盛り上がりましたね！みなさん思った以上に共通点がありましたね。
+ちょうどよいタイミングなので、ここで改めて弊社について少しだけお話しさせてください。3分だけお付き合いください！」</t>
+        </is>
+      </c>
+      <c r="F14" s="119" t="inlineStr">
+        <is>
+          <t>各グループが3つ以上の共通点を発表できている・笑いや驚きの反応が複数回起きている</t>
+        </is>
+      </c>
+      <c r="G14" s="119" t="inlineStr">
+        <is>
+          <t>発表が単調になる → 人事が「それ、深掘りしてもいいですか？」と介入する
+時間が余る → 全体共通点ランキングの解説を丁寧にする
+時間が足りない → 全体共通点ランキングを省略して各グループ発表を優先</t>
+        </is>
+      </c>
+      <c r="H14" s="119" t="inlineStr">
+        <is>
+          <t>6/23（女子4名）は1グループのみなので深掘りトークに時間をかける
+6/30（混合6名）は2グループに分けて発表し合う形式にすると盛り上がりやすい</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="130" customHeight="1">
+      <c r="A15" s="117" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B15" s="118" t="inlineStr">
+        <is>
+          <t>会社説明
+（インプットのみ）</t>
+        </is>
+      </c>
+      <c r="C15" s="117" t="inlineStr">
+        <is>
+          <t>50〜55分
+（5分）</t>
+        </is>
+      </c>
+      <c r="D15" s="117" t="inlineStr">
+        <is>
+          <t>全員が打ち解けて盛り上がった状態のあとに会社説明を届けることで、参加者の受け取り方が変わる（感情一致効果）。
+「楽しかった」という感情が会社への好印象と結びつくベストタイミング。
+アウトプットは一切求めない。3つのキーワードを記憶に残すだけでよい。</t>
+        </is>
+      </c>
+      <c r="E15" s="117" t="inlineStr">
+        <is>
+          <t>【冒頭セリフ（ワークの余韻を活かした言い回し）】
+「みなさんと話していて、こんなに個性豊かな同期が集まったんだなとあらためて実感しました。
+そんなみなさんが入社する会社について、改めて少しだけお伝えさせてください。3分だけお付き合いください！」
+【伝える3点（各1分・計3分）】
+① 業界NO.1の安定性
+「人材派遣業界の中でも建設・インフラ特化で業界シェアトップクラスです。建設インフラは社会インフラそのものなので景気に左右されにくい特性があります。」
+② 本社勤め・選ぶ側
+「皆さんは派遣される側ではなく、派遣する側・コーディネートする側です。毎日スーツで本社出社が基本で、現場仕事ではありません。」
+③ 大手グループの安定感
+「〇〇グループ傘下として、バックアップ体制もしっかりしています。」
+【締めセリフ（クロージングへの橋渡し）】
+「友達や親御さんに"どんな会社？"と聞かれたときこの3つを話すだけで説明になります。覚えておいてくださいね。
+では最後にまとめをして終わりにしましょう！」</t>
+        </is>
+      </c>
+      <c r="F15" s="117" t="inlineStr">
+        <is>
+          <t>ネガティブな反応が出ていない・参加者がうなずいている</t>
+        </is>
+      </c>
+      <c r="G15" s="117" t="inlineStr">
+        <is>
+          <t>説明が長くなる → 必ず5分で切る。詳細は後日メールで補足</t>
+        </is>
+      </c>
+      <c r="H15" s="117" t="inlineStr">
+        <is>
+          <t>説明会資料から該当スライドを最大3枚に絞る。資料を見せすぎない</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="130" customHeight="1">
+      <c r="A16" s="119" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B16" s="120" t="inlineStr">
+        <is>
+          <t>クロージング
+＋次回予告</t>
+        </is>
+      </c>
+      <c r="C16" s="119" t="inlineStr">
+        <is>
+          <t>55〜60分
+（5分）</t>
+        </is>
+      </c>
+      <c r="D16" s="119" t="inlineStr">
+        <is>
+          <t>「またこのメンバーに会いたい」という感情で終わらせる。次のイベントへの期待値を上げ入社までの緩やかなつながりを維持する。アンケートで本音を収集し次回以降に活かす。</t>
+        </is>
+      </c>
+      <c r="E16" s="119" t="inlineStr">
+        <is>
+          <t>【締めセリフ例（そのまま使用可）】
+「今日はありがとうございました！最初はどんな会話になるか少し緊張していたんですが、みなさんのおかげでとても盛り上がりましたね。
+今日だけで〇〇という共通点が見つかったり、△△さんの意外な一面が見えたり、一気に仲間感が出た気がしています。
+次は〇月〇日に対面での顔合わせを予定しています。今度は直接会えるのが楽しみです！
+それまでも何かあれば遠慮なく私に連絡してください。連絡先はチャットに貼りますね。
+では最後にアンケートだけお願いします。1分で終わります！URLをチャットに貼ります。」
+【チャットに貼るもの（事前にコピー準備）】
+□ アンケートフォームURL
+□ 次回日程（テキスト）
+□ 人事担当の連絡先（LINE or メール）
+【アンケート項目（5問・1分以内）】
+① 今日の満足度（5段階）
+② 一番楽しかったコンテンツ（選択式）
+③ 入社に対して不安に思っていることがあれば（自由記述・任意）
+④ 次回も参加したいと思えましたか（Yes/No）
+⑤ 一言感想（任意）</t>
+        </is>
+      </c>
+      <c r="F16" s="119" t="inlineStr">
+        <is>
+          <t>参加者全員がアンケートを送信・次回日程をスケジュール登録</t>
+        </is>
+      </c>
+      <c r="G16" s="119" t="inlineStr">
+        <is>
+          <t>時間オーバーの場合 → 全体共通点ランキングを省略する。クロージング時間は絶対に削らない</t>
+        </is>
+      </c>
+      <c r="H16" s="119" t="inlineStr">
+        <is>
+          <t>クロージング後に5〜10分の任意雑談タイムを設けると帰属意識が上がる</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="111" t="inlineStr">
+        <is>
+          <t>■ グループ割り振り詳細</t>
+        </is>
+      </c>
+      <c r="B17" s="108" t="n"/>
+      <c r="C17" s="108" t="n"/>
+      <c r="D17" s="108" t="n"/>
+      <c r="E17" s="108" t="n"/>
+      <c r="F17" s="108" t="n"/>
+      <c r="G17" s="108" t="n"/>
+      <c r="H17" s="108" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="116" t="inlineStr">
+        <is>
+          <t>日程</t>
+        </is>
+      </c>
+      <c r="B18" s="116" t="inlineStr">
+        <is>
+          <t>規模・構成</t>
+        </is>
+      </c>
+      <c r="C18" s="116" t="inlineStr">
+        <is>
+          <t>参加者</t>
+        </is>
+      </c>
+      <c r="D18" s="116" t="inlineStr">
+        <is>
+          <t>ワーク進行のポイント</t>
+        </is>
+      </c>
+      <c r="E18" s="116" t="inlineStr">
+        <is>
+          <t>担当人事</t>
+        </is>
+      </c>
+      <c r="F18" s="116" t="inlineStr">
+        <is>
+          <t>特記事項</t>
+        </is>
+      </c>
+      <c r="G18" s="116" t="inlineStr"/>
+      <c r="H18" s="116" t="inlineStr"/>
+    </row>
+    <row r="19" ht="90" customHeight="1">
+      <c r="A19" s="120" t="inlineStr">
+        <is>
+          <t>2026/6/23
+11:00〜12:00</t>
+        </is>
+      </c>
+      <c r="B19" s="119" t="inlineStr">
+        <is>
+          <t>4名
+女性のみ</t>
+        </is>
+      </c>
+      <c r="C19" s="119" t="inlineStr">
+        <is>
+          <t>市川 結菜（神奈川大学）
+柳澤 明（東京経済大学）
+荒井 翠（駒澤大学）
+根本 彩花（東京富士大学）</t>
+        </is>
+      </c>
+      <c r="D19" s="119" t="inlineStr">
+        <is>
+          <t>【前半】1グループ全員で共通点を探す。少人数なので深掘りしやすい。共通点の"質"を重視。
+【後半】全体発表は1グループのみなので共通点ごとにエピソードを丁寧に話してもらう。深掘りトークに十分時間をかける。
+【市川】まとめ役 → 発表時のリード役に自然になる
+【荒井】ホスピタリティ高め → 他者を引き出す質問が得意</t>
+        </is>
+      </c>
+      <c r="E19" s="119" t="inlineStr">
+        <is>
+          <t>齋藤（MC）
+もう1名（チャット管理）</t>
+        </is>
+      </c>
+      <c r="F19" s="119" t="inlineStr">
+        <is>
+          <t>全員女性のため共感ベースの会話になりやすい。エピソードの深掘りを積極的に行う。
+会社説明はワーク後のため、全員が打ち解けた状態で聞ける。</t>
+        </is>
+      </c>
+      <c r="G19" s="119" t="inlineStr"/>
+      <c r="H19" s="119" t="inlineStr"/>
+    </row>
+    <row r="20" ht="90" customHeight="1">
+      <c r="A20" s="118" t="inlineStr">
+        <is>
+          <t>2026/6/30
+15:00〜16:00</t>
+        </is>
+      </c>
+      <c r="B20" s="117" t="inlineStr">
+        <is>
+          <t>6名
+女3・男3</t>
+        </is>
+      </c>
+      <c r="C20" s="117" t="inlineStr">
+        <is>
+          <t>富川 哲太（大阪経済大学）
+西山 心町（東海大学）
+吉田 雅野（大東文化大学）
+折笠 未來美（仙台白百合女子大学）
+佐々木 七都（福岡大学）
+本多 諒（九州産業大学）</t>
+        </is>
+      </c>
+      <c r="D20" s="117" t="inlineStr">
+        <is>
+          <t>【前半】2〜3名のブレイクアウトルームに分けて共通点を探す。グループをまたいだ共通点が後半で盛り上がりやすい。
+【後半】グループごとに発表し合う。他グループとの共通点が出たら全体で盛り上げる。
+【富川】野球全国優勝 → 自己紹介で場を沸かせる。グループワークでもムードメーカー
+【本多】ボクサー → 意外な共通点を持っている可能性大。発表で笑いが取れる</t>
+        </is>
+      </c>
+      <c r="E20" s="117" t="inlineStr">
+        <is>
+          <t>齋藤（MC）
+もう1名（チャット管理）</t>
+        </is>
+      </c>
+      <c r="F20" s="117" t="inlineStr">
+        <is>
+          <t>男女混合で共通点の意外性が出やすい。会社説明はワーク後のため、全員が打ち解けた状態で聞ける。</t>
+        </is>
+      </c>
+      <c r="G20" s="117" t="inlineStr"/>
+      <c r="H20" s="117" t="inlineStr"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="111" t="inlineStr">
+        <is>
+          <t>■ 成功させるための5つのポイント</t>
+        </is>
+      </c>
+      <c r="B21" s="108" t="n"/>
+      <c r="C21" s="108" t="n"/>
+      <c r="D21" s="108" t="n"/>
+      <c r="E21" s="108" t="n"/>
+      <c r="F21" s="108" t="n"/>
+      <c r="G21" s="108" t="n"/>
+      <c r="H21" s="108" t="n"/>
+    </row>
+    <row r="22" ht="40" customHeight="1">
+      <c r="A22" s="121" t="inlineStr">
+        <is>
+          <t>✔ カメラON徹底</t>
+        </is>
+      </c>
+      <c r="B22" s="110" t="n"/>
+      <c r="C22" s="117" t="inlineStr">
+        <is>
+          <t>事前メールに「交流が目的なのでカメラONでご参加ください」と明記。当日冒頭でも笑顔でお願いする。強制感を出さず自然に促す。</t>
+        </is>
+      </c>
+      <c r="D22" s="110" t="n"/>
+      <c r="E22" s="110" t="n"/>
+      <c r="F22" s="110" t="n"/>
+      <c r="G22" s="110" t="n"/>
+      <c r="H22" s="110" t="n"/>
+    </row>
+    <row r="23" ht="40" customHeight="1">
+      <c r="A23" s="121" t="inlineStr">
+        <is>
+          <t>✔ 人事が一番楽しむ</t>
+        </is>
+      </c>
+      <c r="B23" s="110" t="n"/>
+      <c r="C23" s="117" t="inlineStr">
+        <is>
+          <t>人事担当者がテンション1.2倍・一番に自己開示する。共通点探しで「私もそれあります！」と積極的に参加すると場が温まる。</t>
+        </is>
+      </c>
+      <c r="D23" s="110" t="n"/>
+      <c r="E23" s="110" t="n"/>
+      <c r="F23" s="110" t="n"/>
+      <c r="G23" s="110" t="n"/>
+      <c r="H23" s="110" t="n"/>
+    </row>
+    <row r="24" ht="40" customHeight="1">
+      <c r="A24" s="121" t="inlineStr">
+        <is>
+          <t>✔ 発表での深掘りが鍵</t>
+        </is>
+      </c>
+      <c r="B24" s="110" t="n"/>
+      <c r="C24" s="117" t="inlineStr">
+        <is>
+          <t>後半の発表で「それって具体的にどういうこと？」と一言深掘りするだけで場の密度が上がる。人事が深掘りの質を担う。</t>
+        </is>
+      </c>
+      <c r="D24" s="110" t="n"/>
+      <c r="E24" s="110" t="n"/>
+      <c r="F24" s="110" t="n"/>
+      <c r="G24" s="110" t="n"/>
+      <c r="H24" s="110" t="n"/>
+    </row>
+    <row r="25" ht="40" customHeight="1">
+      <c r="A25" s="121" t="inlineStr">
+        <is>
+          <t>✔ 会社説明のタイミングを活かす</t>
+        </is>
+      </c>
+      <c r="B25" s="110" t="n"/>
+      <c r="C25" s="117" t="inlineStr">
+        <is>
+          <t>ワーク後の盛り上がった状態のまま会社説明に入ることで学生の受け取り方が変わる。「みなさんと話していて実感した」という一言で感情をつなげてから入る。</t>
+        </is>
+      </c>
+      <c r="D25" s="110" t="n"/>
+      <c r="E25" s="110" t="n"/>
+      <c r="F25" s="110" t="n"/>
+      <c r="G25" s="110" t="n"/>
+      <c r="H25" s="110" t="n"/>
+    </row>
+    <row r="26" ht="40" customHeight="1">
+      <c r="A26" s="121" t="inlineStr">
+        <is>
+          <t>✔ グループをまたいだ共通点を見逃さない</t>
+        </is>
+      </c>
+      <c r="B26" s="110" t="n"/>
+      <c r="C26" s="117" t="inlineStr">
+        <is>
+          <t>後半発表で他グループと共通する内容が出たら「他のグループも！？」と全体に振ることで一体感が生まれる。人事がリアルタイムでメモしておく。</t>
+        </is>
+      </c>
+      <c r="D26" s="110" t="n"/>
+      <c r="E26" s="110" t="n"/>
+      <c r="F26" s="110" t="n"/>
+      <c r="G26" s="110" t="n"/>
+      <c r="H26" s="110" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="19">
+    <mergeCell ref="C25:H25"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C22:H22"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C23:H23"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="C24:H24"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C26:H26"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -4116,7 +5093,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="C20:H20"/>
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A21:B21"/>
@@ -4128,11 +5104,12 @@
     <mergeCell ref="C22:H22"/>
     <mergeCell ref="A13:H13"/>
     <mergeCell ref="C18:H18"/>
+    <mergeCell ref="A17:H17"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A18:B18"/>
     <mergeCell ref="C21:H21"/>
     <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="C20:H20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4993,12 +5970,12 @@
     <mergeCell ref="C24:H24"/>
     <mergeCell ref="A26:B26"/>
     <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C26:H26"/>
+    <mergeCell ref="A5:H5"/>
     <mergeCell ref="C22:H22"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="C23:H23"/>
-    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="C26:H26"/>
     <mergeCell ref="A8:H8"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="A17:H17"/>
@@ -6244,13 +7221,13 @@
           <t>27新卒 内定承諾者向け 顔合わせ企画書（Zoom・60分）　【構成改訂版 v4】</t>
         </is>
       </c>
-      <c r="B1" s="108" t="n"/>
-      <c r="C1" s="108" t="n"/>
-      <c r="D1" s="108" t="n"/>
-      <c r="E1" s="108" t="n"/>
-      <c r="F1" s="108" t="n"/>
-      <c r="G1" s="108" t="n"/>
-      <c r="H1" s="108" t="n"/>
+      <c r="B1" s="122" t="n"/>
+      <c r="C1" s="122" t="n"/>
+      <c r="D1" s="122" t="n"/>
+      <c r="E1" s="122" t="n"/>
+      <c r="F1" s="122" t="n"/>
+      <c r="G1" s="122" t="n"/>
+      <c r="H1" s="123" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="109" t="inlineStr">
@@ -6258,13 +7235,13 @@
           <t>参加者：内定承諾者 各グループ ＋ 人事担当　／　形式：Zoom　／　総時間：55〜60分</t>
         </is>
       </c>
-      <c r="B2" s="110" t="n"/>
-      <c r="C2" s="110" t="n"/>
-      <c r="D2" s="110" t="n"/>
-      <c r="E2" s="110" t="n"/>
-      <c r="F2" s="110" t="n"/>
-      <c r="G2" s="110" t="n"/>
-      <c r="H2" s="110" t="n"/>
+      <c r="B2" s="124" t="n"/>
+      <c r="C2" s="124" t="n"/>
+      <c r="D2" s="124" t="n"/>
+      <c r="E2" s="124" t="n"/>
+      <c r="F2" s="124" t="n"/>
+      <c r="G2" s="124" t="n"/>
+      <c r="H2" s="125" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="111" t="inlineStr">
@@ -6272,13 +7249,13 @@
           <t>■ 設計思想・構成の原則</t>
         </is>
       </c>
-      <c r="B3" s="108" t="n"/>
-      <c r="C3" s="108" t="n"/>
-      <c r="D3" s="108" t="n"/>
-      <c r="E3" s="108" t="n"/>
-      <c r="F3" s="108" t="n"/>
-      <c r="G3" s="108" t="n"/>
-      <c r="H3" s="108" t="n"/>
+      <c r="B3" s="122" t="n"/>
+      <c r="C3" s="122" t="n"/>
+      <c r="D3" s="122" t="n"/>
+      <c r="E3" s="122" t="n"/>
+      <c r="F3" s="122" t="n"/>
+      <c r="G3" s="122" t="n"/>
+      <c r="H3" s="123" t="n"/>
     </row>
     <row r="4" ht="95" customHeight="1">
       <c r="A4" s="109" t="inlineStr">
@@ -6291,13 +7268,13 @@
 会社説明は前半の盛り上がりの直後に「息継ぎ」として差し込む。アウトプットを求めず5分で完結させる。</t>
         </is>
       </c>
-      <c r="B4" s="110" t="n"/>
-      <c r="C4" s="110" t="n"/>
-      <c r="D4" s="110" t="n"/>
-      <c r="E4" s="110" t="n"/>
-      <c r="F4" s="110" t="n"/>
-      <c r="G4" s="110" t="n"/>
-      <c r="H4" s="110" t="n"/>
+      <c r="B4" s="124" t="n"/>
+      <c r="C4" s="124" t="n"/>
+      <c r="D4" s="124" t="n"/>
+      <c r="E4" s="124" t="n"/>
+      <c r="F4" s="124" t="n"/>
+      <c r="G4" s="124" t="n"/>
+      <c r="H4" s="125" t="n"/>
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="111" t="inlineStr">
@@ -6305,13 +7282,13 @@
           <t>■ 全体タイムライン</t>
         </is>
       </c>
-      <c r="B5" s="108" t="n"/>
-      <c r="C5" s="108" t="n"/>
-      <c r="D5" s="108" t="n"/>
-      <c r="E5" s="108" t="n"/>
-      <c r="F5" s="108" t="n"/>
-      <c r="G5" s="108" t="n"/>
-      <c r="H5" s="108" t="n"/>
+      <c r="B5" s="122" t="n"/>
+      <c r="C5" s="122" t="n"/>
+      <c r="D5" s="122" t="n"/>
+      <c r="E5" s="122" t="n"/>
+      <c r="F5" s="122" t="n"/>
+      <c r="G5" s="122" t="n"/>
+      <c r="H5" s="123" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
       <c r="A6" s="112" t="inlineStr">
@@ -6368,8 +7345,8 @@
           <t>◀━━━ 同一ワーク「共通点探し」　前半＝グループ内で探す　/　後半＝全体に発表 ━━━▶</t>
         </is>
       </c>
-      <c r="D7" s="110" t="n"/>
-      <c r="E7" s="110" t="n"/>
+      <c r="D7" s="124" t="n"/>
+      <c r="E7" s="125" t="n"/>
       <c r="F7" s="114" t="n"/>
       <c r="G7" s="114" t="n"/>
       <c r="H7" s="114" t="n"/>
@@ -6380,13 +7357,13 @@
           <t>■ プログラム詳細</t>
         </is>
       </c>
-      <c r="B8" s="108" t="n"/>
-      <c r="C8" s="108" t="n"/>
-      <c r="D8" s="108" t="n"/>
-      <c r="E8" s="108" t="n"/>
-      <c r="F8" s="108" t="n"/>
-      <c r="G8" s="108" t="n"/>
-      <c r="H8" s="108" t="n"/>
+      <c r="B8" s="122" t="n"/>
+      <c r="C8" s="122" t="n"/>
+      <c r="D8" s="122" t="n"/>
+      <c r="E8" s="122" t="n"/>
+      <c r="F8" s="122" t="n"/>
+      <c r="G8" s="122" t="n"/>
+      <c r="H8" s="123" t="n"/>
     </row>
     <row r="9" ht="35" customHeight="1">
       <c r="A9" s="116" t="inlineStr">
@@ -6842,13 +7819,13 @@
           <t>■ グループ割り振り詳細</t>
         </is>
       </c>
-      <c r="B17" s="108" t="n"/>
-      <c r="C17" s="108" t="n"/>
-      <c r="D17" s="108" t="n"/>
-      <c r="E17" s="108" t="n"/>
-      <c r="F17" s="108" t="n"/>
-      <c r="G17" s="108" t="n"/>
-      <c r="H17" s="108" t="n"/>
+      <c r="B17" s="122" t="n"/>
+      <c r="C17" s="122" t="n"/>
+      <c r="D17" s="122" t="n"/>
+      <c r="E17" s="122" t="n"/>
+      <c r="F17" s="122" t="n"/>
+      <c r="G17" s="122" t="n"/>
+      <c r="H17" s="123" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="116" t="inlineStr">
@@ -6978,13 +7955,13 @@
           <t>■ 成功させるための5つのポイント</t>
         </is>
       </c>
-      <c r="B21" s="108" t="n"/>
-      <c r="C21" s="108" t="n"/>
-      <c r="D21" s="108" t="n"/>
-      <c r="E21" s="108" t="n"/>
-      <c r="F21" s="108" t="n"/>
-      <c r="G21" s="108" t="n"/>
-      <c r="H21" s="108" t="n"/>
+      <c r="B21" s="122" t="n"/>
+      <c r="C21" s="122" t="n"/>
+      <c r="D21" s="122" t="n"/>
+      <c r="E21" s="122" t="n"/>
+      <c r="F21" s="122" t="n"/>
+      <c r="G21" s="122" t="n"/>
+      <c r="H21" s="123" t="n"/>
     </row>
     <row r="22" ht="40" customHeight="1">
       <c r="A22" s="121" t="inlineStr">
@@ -6992,17 +7969,17 @@
           <t>✔ カメラON徹底</t>
         </is>
       </c>
-      <c r="B22" s="110" t="n"/>
+      <c r="B22" s="125" t="n"/>
       <c r="C22" s="117" t="inlineStr">
         <is>
           <t>事前メールに「交流が目的なのでカメラONでご参加ください」と明記。当日冒頭でも笑顔でお願いする。強制感を出さず自然に促す。</t>
         </is>
       </c>
-      <c r="D22" s="110" t="n"/>
-      <c r="E22" s="110" t="n"/>
-      <c r="F22" s="110" t="n"/>
-      <c r="G22" s="110" t="n"/>
-      <c r="H22" s="110" t="n"/>
+      <c r="D22" s="124" t="n"/>
+      <c r="E22" s="124" t="n"/>
+      <c r="F22" s="124" t="n"/>
+      <c r="G22" s="124" t="n"/>
+      <c r="H22" s="125" t="n"/>
     </row>
     <row r="23" ht="40" customHeight="1">
       <c r="A23" s="121" t="inlineStr">
@@ -7010,17 +7987,17 @@
           <t>✔ 人事が一番楽しむ</t>
         </is>
       </c>
-      <c r="B23" s="110" t="n"/>
+      <c r="B23" s="125" t="n"/>
       <c r="C23" s="117" t="inlineStr">
         <is>
           <t>人事担当者がテンション1.2倍・一番に自己開示する。共通点探しで「私もそれあります！」と積極的に参加すると場が温まる。</t>
         </is>
       </c>
-      <c r="D23" s="110" t="n"/>
-      <c r="E23" s="110" t="n"/>
-      <c r="F23" s="110" t="n"/>
-      <c r="G23" s="110" t="n"/>
-      <c r="H23" s="110" t="n"/>
+      <c r="D23" s="124" t="n"/>
+      <c r="E23" s="124" t="n"/>
+      <c r="F23" s="124" t="n"/>
+      <c r="G23" s="124" t="n"/>
+      <c r="H23" s="125" t="n"/>
     </row>
     <row r="24" ht="40" customHeight="1">
       <c r="A24" s="121" t="inlineStr">
@@ -7028,17 +8005,17 @@
           <t>✔ 発表での深掘りが鍵</t>
         </is>
       </c>
-      <c r="B24" s="110" t="n"/>
+      <c r="B24" s="125" t="n"/>
       <c r="C24" s="117" t="inlineStr">
         <is>
           <t>後半の発表で「それって具体的にどういうこと？」と一言深掘りするだけで場の密度が上がる。人事が深掘りの質を担う。</t>
         </is>
       </c>
-      <c r="D24" s="110" t="n"/>
-      <c r="E24" s="110" t="n"/>
-      <c r="F24" s="110" t="n"/>
-      <c r="G24" s="110" t="n"/>
-      <c r="H24" s="110" t="n"/>
+      <c r="D24" s="124" t="n"/>
+      <c r="E24" s="124" t="n"/>
+      <c r="F24" s="124" t="n"/>
+      <c r="G24" s="124" t="n"/>
+      <c r="H24" s="125" t="n"/>
     </row>
     <row r="25" ht="40" customHeight="1">
       <c r="A25" s="121" t="inlineStr">
@@ -7046,17 +8023,17 @@
           <t>✔ 会社説明の5分を厳守</t>
         </is>
       </c>
-      <c r="B25" s="110" t="n"/>
+      <c r="B25" s="125" t="n"/>
       <c r="C25" s="117" t="inlineStr">
         <is>
           <t>「後半の発表が残っている」という状態が参加者を前のめりにさせる。会社説明が長引くとその効果が消える。5分を必ず守る。</t>
         </is>
       </c>
-      <c r="D25" s="110" t="n"/>
-      <c r="E25" s="110" t="n"/>
-      <c r="F25" s="110" t="n"/>
-      <c r="G25" s="110" t="n"/>
-      <c r="H25" s="110" t="n"/>
+      <c r="D25" s="124" t="n"/>
+      <c r="E25" s="124" t="n"/>
+      <c r="F25" s="124" t="n"/>
+      <c r="G25" s="124" t="n"/>
+      <c r="H25" s="125" t="n"/>
     </row>
     <row r="26" ht="40" customHeight="1">
       <c r="A26" s="121" t="inlineStr">
@@ -7064,17 +8041,17 @@
           <t>✔ グループをまたいだ共通点を見逃さない</t>
         </is>
       </c>
-      <c r="B26" s="110" t="n"/>
+      <c r="B26" s="125" t="n"/>
       <c r="C26" s="117" t="inlineStr">
         <is>
           <t>後半発表で他グループと共通する内容が出たら「他のグループも！？」と全体に振ることで一体感が生まれる。人事がリアルタイムでメモしておく。</t>
         </is>
       </c>
-      <c r="D26" s="110" t="n"/>
-      <c r="E26" s="110" t="n"/>
-      <c r="F26" s="110" t="n"/>
-      <c r="G26" s="110" t="n"/>
-      <c r="H26" s="110" t="n"/>
+      <c r="D26" s="124" t="n"/>
+      <c r="E26" s="124" t="n"/>
+      <c r="F26" s="124" t="n"/>
+      <c r="G26" s="124" t="n"/>
+      <c r="H26" s="125" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="19">
@@ -7089,8 +8066,8 @@
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A21:H21"/>
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A5:H5"/>
     <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A5:H5"/>
     <mergeCell ref="A8:H8"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="A17:H17"/>
